--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E57926D-0E7C-4BEB-AF6C-BF29D009AD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E34D6F-2ACB-4A1D-92F0-932BD8BB6AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="257">
   <si>
     <t>youtube_link</t>
   </si>
@@ -7611,7 +7611,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7620,7 +7620,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7650,10 +7649,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7993,7 +7988,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>178</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -8001,653 +7996,653 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" t="s">
         <v>107</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" t="s">
         <v>108</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>109</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" t="s">
         <v>110</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" t="s">
         <v>111</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" t="s">
         <v>112</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" t="s">
         <v>113</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" t="s">
         <v>114</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" t="s">
         <v>115</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" t="s">
         <v>116</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" t="s">
         <v>117</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" t="s">
         <v>118</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" t="s">
         <v>119</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" t="s">
         <v>120</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" t="s">
         <v>121</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" t="s">
         <v>122</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" t="s">
         <v>123</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" t="s">
         <v>124</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" t="s">
         <v>125</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" t="s">
         <v>126</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E21" s="6"/>
+      <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" t="s">
         <v>127</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="A23" t="s">
         <v>128</v>
       </c>
       <c r="B23" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" t="s">
         <v>129</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" t="s">
         <v>130</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E25" s="6"/>
+      <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" t="s">
         <v>131</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="5" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" t="s">
         <v>132</v>
       </c>
       <c r="B27" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E27" s="6"/>
+      <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" t="s">
         <v>133</v>
       </c>
       <c r="B28" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" t="s">
         <v>134</v>
       </c>
       <c r="B29" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" t="s">
         <v>135</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" t="s">
         <v>136</v>
       </c>
       <c r="B31" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" t="s">
         <v>137</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="A33" t="s">
         <v>138</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="A34" t="s">
         <v>139</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="5" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" t="s">
         <v>140</v>
       </c>
       <c r="B35" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" t="s">
         <v>141</v>
       </c>
       <c r="B36" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="A37" t="s">
         <v>142</v>
       </c>
       <c r="B37" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="5" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="A38" t="s">
         <v>143</v>
       </c>
       <c r="B38" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" t="s">
         <v>144</v>
       </c>
       <c r="B39" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="E39" s="6"/>
+      <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" t="s">
         <v>145</v>
       </c>
       <c r="B40" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E40" s="6"/>
+      <c r="E40" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E40" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
@@ -8660,436 +8655,557 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" t="s">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" t="s">
         <v>25</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" t="s">
         <v>26</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
         <v>27</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" t="s">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" t="s">
         <v>30</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" t="s">
         <v>31</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="B31" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="B35" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="B36" t="s">
         <v>37</v>
       </c>
+      <c r="C36" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="B37" t="s">
         <v>38</v>
       </c>
+      <c r="C37" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="B38" t="s">
         <v>39</v>
       </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="B39" t="s">
         <v>40</v>
       </c>
+      <c r="C39" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" t="s">
         <v>41</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>41</v>
       </c>
     </row>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E34D6F-2ACB-4A1D-92F0-932BD8BB6AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D7E547-9628-4C5F-8E3F-857AB0BD8698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
     <sheet name="Transcripts" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Transcripts!$A$1:$D$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WOOM Archive'!$A$1:$E$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="262">
   <si>
     <t>youtube_link</t>
   </si>
@@ -7525,6 +7526,1480 @@
     &lt;/ul&gt;
   &lt;/div&gt;
 &lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:00 Darius: It's never happened to me in my whack, *****.
+00:00:03 Jordan: It's like, chat in my chop.
+00:00:07 Darius: I was like, this is it. Welcome to Out the Trunk with Jordan and Darius. My name is Darius. That's Deez. I love the area on all socials. And I'm Jordan.
+00:00:14 Jordan: That's Jordan to be writing on all socials.
+00:00:16 Darius: This is our segment we've titled What's On Our Mind, where we discuss what's on our mind, what we've been saying on the internet, all of the above. So graphic going around the internet, We're going to post it here so the audience can follow along. But you got to settle this debate. We got the coffee up there. We got the toast up there. We got the steak up there. Which numbers are you choosing?
+00:00:39 Jordan: So I'm not a big coffee guy, to be honest. I drink coffee like maybe once a month. So I'd go for coffee. I'd go probably a four or five. For toast, I'm going 4. And then on steak, I'm going I'm going to.
+00:01:00 Darius: Okay. Okay. Follow up question. You what occasions do you drink coffee on? If it's only if it's so infrequent, it has to be for some reason.
+00:01:09 Jordan: Yeah, it's just if I'm just like really, really dead at work or if I need to like work through lunch or if like I drink coffee today. I had a cup today at like 430 because I had to power through some cases and then I had to do the rewatch and get everything ready, you know, for the pod and stuff. Usually I nap before the pod, but today I had to take care of some other stuff. So, I just use it as like an energy drink, basically.
+00:01:33 Darius: Fair enough. One for me, five for me, two for me. I drink coffee every morning. I have a giant Yeti that I refill. I probably go through a pot a day. So I wake up, have my 4 cups of water to start the day. And then I'm running the coffee while I do that and I fill up my Yeti. Also, I only run the, so I fill up the coffee pot halfway. So it's like half a pot of coffee that I drink myself, but I fill up the Yeti like twice and it keeps it hot all day.
+00:02:07 Jordan: Okay.
+00:02:08 Darius: You know, free promo for Yeti. Great product. Five on the toast. I like my toast burnt. I just, I want it just right before it's inedible. It's right where I want my toast and I want the egg to be not liquid. I want the the white set, but I want the yolk running. So solid over medium with the yolk, the rich yolk over that burnt *** toast, elite eats right there. If I have to pick one, it's medium rare number two, but it depends on the steak. Like ribeye, I like to have that medium because anything colder to me, the fat cap doesn't render and you're just eating like cold fat. But like a filet, I can go up to rare, but it just split in the pole. But like if Either strip or a skirt steak. I'm going medium rare. So, you know, that's that's my rundown. One, five and two. So audience. Yeah, I'm.
+00:03:06 Jordan: Oh, go ahead.
+00:03:07 Darius: No, I was going to say the audience can reach out and let us know what numbers they would pick.
+00:03:12 Jordan: Yeah, I'm with the burnt ****. That's more like hot dogs, sausage, stuff like that. I like salmon a little bit blackened from time to time. But it depends on how I feel.
+00:03:24 Darius: I also love a burnt hot dog. Even even even a burger, man. I'm not turning away.
+00:03:30 Jordan: Yeah, I'm not mad at that.
+00:03:31 Darius: I'm not gonna lie. I'm not really a salmon guy. I don't I don't like any salmon, but really interesting. No, I'm if I'm getting fish, it's if it's in a restaurant, I mean, it just depends. But like flounder cod. I'll even eat like a tuna fin before I'll do a salmon. Just not my thing.
+00:03:54 Jordan: Really? Is it the texture or?
+00:03:56 Darius: Just the flavor. It just tastes gross. So I will say my first experience with salmon was at Red Lobster, so that might not count. It might have colored. And I have had salmon prepared for me by a woman and it was fine. I didn't tell her I don't eat salmon. She just cooked it. And so I ate it because that was a polite thing to do and it wasn't terrible, but it's not my go-to. So. All right, man, you hear about the Tuskegee dress code?
+00:04:28 Jordan: I did hear a little bit about it. I saw some of the discourse on TikTok and Twitter over the last few days.
+00:04:34 Darius: So it just is for the audience to be aware. Basically, it's a long standing dress code, but I guess it was like time to reiterate what, you know, every so often, you know how your job has a dress code. People get a little lax. They remind you to put a dress code or whatever.
+00:04:47 Jordan: Yeah.
+00:04:47 Darius: So I mean, long and the short, no bonnets, no durags, no pajamas. I think honestly, that's really no bed slippers. Like basically don't look like you don't wear what you wore to sleep outside. So what are your thoughts on that?
+00:05:04 Jordan: I mean, I went to HBCU and people wore slippers and pajama pants and sweatpants and joggers and all this up to class. I mean, I think it really depended more so on the professor, to be honest. I think it was more so at their discretion. Like some professor didn't really want you to wear hats, you know, **** like that. So I mean, I was, in general, I'm cool with the dress code. It's not, you know, the end of the world. Until I saw Reddit somewhere that they have it applies to like the calf too. I think the calf should be a little more lax. I think that's kind of ****** ** and not ****** **. I think that's just doing a little bit too much to be honest. That's you know, that's the kitchen.
+00:05:40 Darius: Yeah, that's the kitchen and decided they have a kitchen in their dorms. And so to me, the classroom is like going to work. So ain't nobody told me to put on a suit, just jeans and a t-shirt. I'm sorry, but you're not gonna give me too riled up over making people wear jeans and a t-shirt.
+00:05:55 Jordan: Yeah, the bonnets, like the slippers, I think is a bit much like, you know, whatever, but the bonnets and the do-rags, I kind of understand.
+00:06:02 Darius: I'm just not, I'm not gonna march on Semo over that. It's like they made you wear jeans and a t-shirt. You know, it would be one thing like, it's okay. Yeah, if they said slacks in a coat, I mean, all right. Y'all doing a lot for, you know, 8 AM biology course, but facts, but yeah, the calf like, okay, walking to.
+00:06:25 Jordan: Pick up some food.
+00:06:26 Darius: That's doing too much. That is doing.
+00:06:28 Jordan: Yeah, man.
+00:06:29 Darius: To me, that's like getting dressed to take out the garbage. Right. No one does that. You know, it's like, come on, man. You know, so you know how the Internet is. Everyone has to be super extreme about it.
+00:06:40 Jordan: Yeah.
+00:06:40 Darius: I don't think it's respectability politics to Yeah, that's really nice.
+00:06:48 Jordan: It's not crazy. It didn't say no ripped jeans or anything like that.
+00:06:51 Darius: Yeah, it's like no chains, no, sneakers, no. It's literally don't look like you woke up and came to class. Right.
+00:06:59 Jordan: It's basically just don't look like you just brush your teeth and went to class.
+00:07:05 Darius: Also, like a primary function of college beyond educating students is preparing them for the world.
+00:07:10 Jordan: For the real world.
+00:07:11 Darius: And look, I'm. I mean, like I said, it's not overly onerous. It's pretty straightforward. And in real world, you do have to put on clothes to go outside. Right.
+00:07:26 Jordan: You know, it's like, unless you're going to like Walmart or the airport. Those are the two exceptions pretty much.
+00:07:33 Darius: I'm the way the things people wear to the airport, they're doing too much too. I really don't. I want to know what jeans people are buying that are so uncomfortable that you just can't. Do they fit you? Is that maybe the problem? Yes, if your clothes don't fit, they will be uncomfortable, but your jeans should not be overly restrictive.
+00:07:57 Jordan: I'm not gonna lie, it does feel like one of those things where like, it's like, One person said it and then we already started to believe it. Cause when I have long drives, I'm like, I can't wear jeans on a long drive. So I wear like sweatpants or basketball shorts. And then I'm like, but I can drive in jeans. I drive in jeans every day.
+00:08:12 Darius: My jeans are comfortable, man. I don't wear baggy jeans. I wear jeans that fit me and I don't feel restricted when I wear my jeans. I just think people should buy clothes that fit. And also just It's a very childish mindset that comfort should be the priority any and all times. Like every everywhere.
+00:08:30 Jordan: Yeah.
+00:08:31 Darius: Sometimes you have to prioritize other things other than being maximally comfortable. We can't put your couch in the airport. Like we have to.
+00:08:38 Jordan: Right. Yeah, there's a fine line because it's like, you know, like going out as a black person is like can be challenging because, you know, every some certain place have their like, no, especially, you know, downtown going south. But then there's like, I was at the bar like a couple weeks ago when a guy walked in with like, hey, you gotta go to your car and put a shirt on. You know what I mean? Like some **** you do have to do.
+00:09:05 Darius: Yeah. And it's like, I listen, we went through the boat shoes in the club era. I get it. But you can't just throw the same accusation on everything. This HBCU is not being racist.
+00:09:19 Jordan: No, Now there is a classism aspect to certain HBCUs, but I don't think this falls under that category.
+00:09:28 Darius: College is in and of itself elitist. Yeah, true, The vast majority of people don't go to college. So yes, we are, in theory, you go to college to join the elites. That's, yes, that is. You're trying to transcend class. So of course it's elitist. That's the point. And so, you know, it's okay to have some sort of baseline decorum. Yeah. And also like as black people, didn't we all, I thought we liked putting that **** on. Like what happened to this?
+00:09:56 Jordan: That's, yeah, that is true. We do be like, that's kind of our thing.
+00:10:00 Darius: Like when do we want to start going places looking crazy? I was raised to go and go anywhere looking crazy.
+00:10:04 Jordan: Yeah.
+00:10:05 Darius: You know, it's just.
+00:10:06 Jordan: And if you did, you saw us when you knew you kind of hid so they didn't see you looking crazy.
+00:10:11 Darius: It was like, make sure you got on a clean draw just in case you get in an accident. it was like, it was like the whole thing is like, you don't want anyone to see you. don't know who you're going to run into and so on and so forth. So I don't know. Like I just, I'm splitting the middle of this one. It's a fairly moderate policy. I'm a fairly moderate person. So I'm okay with it. Like it's fine to, you know, as I'm reiterating earlier, like you're trying to introduce some to adulthood with some guardrails so that the mistakes aren't catastrophic. And like, it's okay to tap a young man on the shoulder and be like, hey, you know, you look, you can't, like, we need to dress it up a little bit. Better to tell them at 20 than the first job interview they have, they blow it 'cause they look crazy.
+00:10:52 Jordan: Correct. Or even like, I've had jobs where people like got sent home to change their clothes 'cause they were not mentioned dress code. And like the first two weeks of the job, you know?
+00:11:04 Darius: I mean, and it's just, it, if it was suited and booted, I would have a, I would understand, but if you can get away with jeans and a t-shirt, you're not going to get much pushback from me on the dress code. Cause to me, that's barely a dress code.
+00:11:18 Jordan: If they had said like no hats or something, I'd be like, okay, that's crazy. You know what I mean?
+00:11:22 Darius: Or, you know, like you said, no ripped jeans, no chains, no jerseys, no solid colored t-shirts.
+00:11:30 Jordan: Yeah.
+00:11:31 Darius: So Yeah, I don't know. We're going to call that one down the middle and say, I'm with the Tuskegee University on that one. As long as, and clearly they wouldn't even do this if it wasn't getting outrageous, you know?
+00:11:43 Jordan: Clearly somebody pulled up to class wearing nothing.
+00:11:47 Darius: I had a friend who was a teacher who was like, we had to get their parents a dress code and tell them to stop showing up smelling like weed.
+00:11:53 Jordan: Yeah, see, that's crazy. That's nice.
+00:11:54 Darius: Like how you go show up to your kids elementary school smelling like weed? Like you.
+00:11:58 Jordan: That's really disrespectful.
+00:12:00 Darius: The people we should like the mom sometimes we shown up barely just draws just like bare like the shorts.
+00:12:08 Jordan: Yeah, I've seen it.
+00:12:11 Darius: That's like you. This is your child's. You want your child's friends to see you like this.
+00:12:15 Jordan: You see your ***?
+00:12:20 Darius: A lot better.
+00:12:20 Jordan: No, I hear you. And it's like, you know, we can't, we got to keep it called. We've got to keep, keep it consistent across the board because we can't, there's a whole trend of like the teacher influencers where some of them are posting thirst trap ****. It's like, well, who are you out of trap? Exactly. Like it's very predatory, you know, or predatory leaning. And like, you know, we can't say that. And then on one hand also be like, oh, if you're in college, someone who are going to be educators, not instill it across the board. You know what I mean?
+00:12:44 Darius: Listen, and some of I don't know, you don't want to police women's dress, of course, but The teacher stuff. Don't tell me the only thing you can wear to class is a body con dress. Like I just don't.
+00:12:55 Jordan: Yeah. The teacher outfits is crazy because it's like, okay, there's a difference between like, just that's your body type.
+00:13:01 Darius: And then of course.
+00:13:02 Jordan: Does it have to be that short? Does it like, do you have to turn around in your Instagram post so we can see your whole body? I don't know.
+00:13:07 Darius: Also, just like there are code every body type for different occasions. And please, I just do not believe there are no professionally appropriate clothing for curvy women. Like, I just don't buy that.
+00:13:21 Jordan: Yeah. I've never seen Joe Scott look crazy. Yeah.
+00:13:24 Darius: You know, and no one's saying you got to pull up in a moo moo, but it's like, there is, I just hate when people go to the extremes. Like, it's like, okay, but you know what we're talking about. No one's telling them to, you know, dress for a job interview. We're just telling them don't dress like for a camping trip, you know? Right. All right. You want to head into work life balance.
+00:13:49 Jordan: Yeah, I was talking to Louis a couple weeks ago about just like the, struggle of like trying to juggle all the things you need to have a full like life outside of work and then while also being high performing at work at the same time. And there are weeks where it feels like, okay, this week I can do get one or two of those things done. And maybe next week I'll get three out of five done, **** like that. And it makes me wonder like, is it really possible to have a full work-life balance? Like to excel at work while also excelling in whatever your goals and hobbies are outside of work at the same time?
+00:14:23 Darius: I'm reminded of that tweet that's probably been stolen 10 times over and it was like, The amount of work it requires for me to like succeed at my job and keep a mid-body is just outrageous. Yeah, right? Do you know how hard it is for me to just be like a performing employee and keep a mid-body? Right. It's hard, man. It's one of my favorites.
+00:14:48 Jordan: I'm avoiding obesity and unemployment one day at a time.
+00:14:52 Darius: It's like, dude, the amount of times I have to work out a week, I gotta do it again tomorrow and then the day after never stops. And it's like, on my office days, I get up 630, just lay in bed, ******* around on the internet till seven, in the office about 730. And, you work until 4 o'clock and then you go to the gym and you get home and it's like 630 and it's like, yeah. Okay, I still got to cook something. And that just goes into like the keeping a mid body because I could easily hop a grub hub, but I have to cook something because I don't want to kill the workout I just did. Right now it's eight o'clock and I've had no time for myself. Correct. It's true. It is an ever a never ending cycle of responsibilities, you know, so.
+00:15:42 Jordan: Yeah, it's like, like, this year, my main focus really just been like, work, the pod, the gym, and then reading and working on my writing and my poetry and stuff. That's pretty much I try to keep it very simple. And there are weeks where I'm like, okay, I've read a lot and I did really well at work, but I did not get a lot of workouts in. Or did a lot of writing, got a lot of workouts in, and read nothing. I'm always missing out on something. And then next week I'm like, oh, I got to pick up on that. And then because I catch that ball, I drop this one.
+00:16:19 Darius: Yeah, what helps and I know people don't really want to hear this. It helps it like I just if you don't watch a lot of TV, you'd be surprised how much time you get back not watching TV. And don't get me wrong, I watch TV, I watch movies, all that stuff. But just the scrolling and the TV watching, you can get a lot of time back then, but it's hard, you know, because it's like after work and working out and cooking, you know, It's like if I want to read, that's another cognitive burden. Even if I want to watch a movie, depending on the movie, that's a cognitive burden. And I'm just tired of making decisions for the day. I just want, that's why I don't like streamers. I miss when I turn the TV on and I watch what was on the TV, because that was one less decision I had to make. And now it's like I turn on Netflix and like, I got to do something else.
+00:17:11 Jordan: You're bombarded with options.
+00:17:13 Darius: And they're all bad. And so, you know, so I agree. It's hard, but you got to, you know, the weekends are the weekends help. The weekends are, you know, for your free time. And, you know, we go out on weekends and that's kind of like me. I almost feel like I'm buying the time back, you know, on the on the weekends. Right. pop out to a restaurant, have some greasy tacos, some cheese fries, and that's like a reward for the five pieces of chicken and rice meals I had throughout the week. And you have a couple of beers and, you know, it gives you something to look forward to and it gives you something that keeps you disciplined during the week. But, you know. it's a lot of work to be performing at work and keep a mid-body.
+00:17:57 Jordan: It's really ******* hard, dude. It's like, I mean, it's like, and it's like, there's Will Smith Cole where he's like, one night out can **** ** the next 10 days of your life. And it really does feel like that, like I, you know, I remember when the Canes won, you know, when I went crazy the night before, then that night, and then that Monday at work, I was dead, you know. So then Tuesday, they were like, what's up with your performance? And then I'm like, oh ****. And then so ramping up my performance, which means I'm more tired from work, which means I wasn't really working out because I felt bad about not working out. I was like, oh, I got to go super hard in reading or whatever other hobbies and **** I need to get done. But because you put that much pressure on yourself, you really don't want to do it then. So you don't do that. So then you shame yourself. That's another week of productivity you just lost.
+00:18:45 Darius: Yeah. That's why I I like football because it kind of gives me, it kind of grounds my Sunday. And like, you know, the Vikings game, I watched that, but like the four o'clock game, I can do things around the house. I can get ready and sort of transition. It's like a soft transition into responsibility after, you know, being a degenerate on Friday and Saturday. So mostly just Saturday these days. Honestly, Fridays, I've just been kind of chilling. I've been playing video games and different things like that. It's hard.
+00:19:18 Jordan: It is. It's funny. I was at my little cousin's graduation party like a month ago and we were talking about like, just life and ****. And I was like, when I was a kid, my dad would always tell me like, you have strict parents and they're like, when you get your own house, you can do whatever you want, all that kind of **** whatever. And I remember my dad would be like, well, I can do whatever I want because I'm an adult. He's like, when you turn 18, you can do whatever you want. So my whole life was like, I'm going to turn, I just want to turn 18. That's all I want to do in life. And now I can do whatever I want. And it sucks sometimes.
+00:19:47 Darius: It's, yeah, the unlimited choices. It's kind of, we've learned that it's a little overrated, Right. It was easier to stay in shape when your food options were what was in your fridge. It was easier to, you read more books when TV was just like the 30 channels and you've seen every episode of Market.
+00:20:06 Jordan: And if you didn't read this book, you're gonna fail a class.
+00:20:09 Darius: Correct. And so, It's just, you know, little things I block off time. You know, I try to block off time where, you know, a couple of times a week from, you know, seven to eight, it's just, you know, I'm reading or I'm watching a movie or, you know, just like I'm going through like there was The Hollywood Reporter released a list of like 25 greatest documentaries of all time. I hadn't seen 23 of them, you know, I only seen The O.J. Simpson one and the Ali Frazier Rumble and the We Were Kings. I think that's the name of it.
+00:20:45 Jordan: Oh, okay.
+00:20:46 Darius: But I didn't see the other 23. Half of them aren't even in English. And I'm like, you know what? That's a task. That is something for me to do in my downtime. I watched, it was like a 40 minute Holocaust documentary in a different language with English subtitles and like can't scroll your phone. You watch something with subtitles.
+00:21:05 Jordan: Right.
+00:21:06 Darius: And But it was like released in 1956, so it's a lot slower. And the picture quality was amazing, which I was kind of shocked about. I went into Googling about that. And apparently analog film holds up a lot better than like you will see movies made in like the 40s and 50s actually look better than movies made in the 80s and 90s because it was analog.
+00:21:27 Jordan: That is true.
+00:21:28 Darius: Did not know that. And so, yeah, so it's like I watch TV, but like I watch TV in a good way. You have to kind of find the wins and the margins that way. But working on that 25 list, it's a lot of those don't look that good, but we're going to get through it. Most of them are under 2 hours. So it's like, even if it's bad, it's a bad, I've watched a bad movie before. So I want to head into, did you see the tweet that went viral about the lady with the gift?
+00:21:57 Jordan: Yeah, her mom told her she should. Let me quote it here.
+00:22:04 Darius: End quote, I was taught, if you're dating and you get to a third date with the man, you're supposed to bring him a gift to show that you are interested in the situation too, and to show appreciation for him paying for the dates. But maybe that's not the standard. And I just want to know what planet she's from, because I've never heard.
+00:22:20 Jordan: Yeah, it's not what these women are doing.
+00:22:27 Darius: I like to think I'm a decent date. I've never.
+00:22:32 Jordan: No, I've never gotten a third date gift.
+00:22:34 Darius: I think I would be, I think I would literally blush if so. I'd be like, will you marry me? I've never had anyone be this nice to me before.
+00:22:47 Jordan: That's crazy. It brings to mind that Chris Rock joke where it's only women, children, their dogs are loved unconditionally. But honestly, for the worst one, when I read the tweet, I was like, I had to read it again to make sure I read it right. I was like, that's not, that's not real. Or she's lying.
+00:23:09 Darius: All the men in the comments are like, you got any sisters? Could you imagine on a third day she like bought you Madden? I would like, I think I might cry. I mean, it would be like, who sent you and where have you been all my life?
+00:23:24 Jordan: In the words of the great meat meal. I used to pray for times like this. It's. See, I don't know. I feel like I'd maybe be a little, like, scared if someone did that. I don't feel like I don't want to say, like, love bombing, but it feel a little like, I don't know, you know?
+00:23:43 Darius: Third date. I mean, by by then, Yeah, I mean, listen, I would be flattered.
+00:23:51 Jordan: But that is very, that is very kind. That's very, that's a very kind gesture though.
+00:23:56 Darius: I mean, it's far beyond a kind gesture. It is.
+00:23:59 Jordan: Yeah.
+00:24:00 Darius: You know, I would feel, you know, I was like, this never happened to me. Am I a whack *****? Am I a whack *****?
+00:24:06 Jordan: It's like, Chet, am I chopped?
+00:24:09 Darius: Yeah, well, I was like, this is, I don't, there's a whole parallel dating universe that I don't know existed.
+00:24:15 Jordan: Yeah, I've never heard of that. I'm actually about, I'm about to hit up my homegirls like, hey, step your game up.
+00:24:20 Darius: Man, it's, you know, it is time. We are, we're going to, what was her name again? Let me find her. If she's a real person. She's not a blue check.
+00:24:29 Jordan: She's not a blue check. So. Okay.
+00:24:30 Darius: So that means it's probably in the United States. She's not a blue check. But the key spelled like Megan, the key baby. You are a lovely lady. And I wish you all the best in all of your endeavors. And I'm sure the line is long because that profile picture looks pretty good. So.
+00:24:50 Jordan: OK, beautiful gowns, beautiful gowns. I'm going to get into your next topic. Yeah. What was it?
+00:24:59 Darius: Classic movies.
+00:25:00 Jordan: Oh, classic. OK, yeah. So we were hanging out at the bar Friday and I was joking around with Luis and I was like, you know, doing the The Goodfellas, I'm funny, how I'm a clown, I'm Yuzu. And he thought I was like talking **** and I was like, dude, it's Goodfellas. You haven't seen Goodfellas? He's like, no, I haven't. I'm like, that's crazy. So it got me to think about classic movies that I've never seen before or that you've never seen before. Do you have any?
+00:25:24 Darius: I've never seen a scene of either the Lord of the Wings or Star Wars.
+00:25:28 Jordan: Okay.
+00:25:29 Darius: Not not a single frame of any of them.
+00:25:31 Jordan: You're going to hear from a friend of the show about that.
+00:25:35 Darius: She she we're talking about the same friend. She reposted a tweet about so it was like, you know how they like the original video. Then the person comes on and talk **** later. So the original video was some lady like, you know, I'm going over to this boy's house to watch Lord of the Rings. He knows, right? And then it cut to this dude who was like, I know you're going to watch all three. He was like, Oh, yeah, He looked like an anime dude. And he was like, he was like, we're going to watch all of these movies. And you know, and I was like, I know exactly. And I thought that at the time I was like, I have not seen a single frame of a Lord of the Rings movie. I will say of the two, I'm more inclined to watch Lord of the Rings because that seems more my speed. Star Wars, just nothing about that lips appealing to me.
+00:26:21 Jordan: Okay, interesting. Okay.
+00:26:22 Darius: How about you?
+00:26:24 Jordan: Yeah, I got a few. So I've seen the first Star Wars or I've seen the first one and then I've seen Bits and Pieces of the Others. I saw the first Lord of the Rings, but I never saw the other two. I actually was talking to somebody about that trilogy the other day, so I might get eventually I'll get to that. Classic great moves I've never seen before.
+00:26:41 Darius: Well, first, did you like them? Are they like as esteemed as it is?
+00:26:45 Jordan: Yes.
+00:26:45 Darius: Okay. I like the first one.
+00:26:48 Jordan: Yeah, I did. I liked the first one, first Lord of the Rings. I just never got to it. They're long ******* movies and it was like a Sunday and I just was busy and got bored or whatever. What's the other one we were just talking about? Star Wars.
+00:26:58 Darius: Star Wars.
+00:26:59 Jordan: There's like 10 of them. I just didn't know which order to watch them in. So I just got overwhelmed and I just quit.
+00:27:04 Darius: It's a daunting task.
+00:27:06 Jordan: Right? It's like 50 years of movies.
+00:27:09 Darius: And like the problem with those movies is like What made them so revolutionary is in part the special effects that aren't that special to you in 2020.
+00:27:18 Jordan: Look like trash today.
+00:27:19 Darius: No, I the Regal sometimes does like, you know, classic rewatches. And I went and saw the matrix that I had seen it before. And I was just like, I don't get it until someone told me, well, the the special effects is what kind of makes the movie go. Right. And they're not special in 20. I think I thought it was 2024.
+00:27:37 Jordan: Right.
+00:27:38 Darius: What were yours though?
+00:27:40 Jordan: I've never seen A Clockwork Orange. I haven't seen a lot of Kubrick stuff. I never finished Citizen Kane. I think I saw the first like 20 minutes when I was in college. North by Northwest, never saw that. The original Planet of the Apes, the first one, I'd seen it in parts, but I've never seen it. I haven't seen it cover to cover. This one I may lose my black card for. I'll do it in advance. And I hope my parents don't see this. I have never seen from cover to cover do the right thing.
+00:28:11 Darius: Ooh, if we're losing black cards, I've never sat down and watched Boys in the Hood from front to back. What? No, I haven't.
+00:28:21 Jordan: That's crazy.
+00:28:22 Darius: I have seen it in different spots, but like, my first minister society is like iconic to me. Right. Like, I don't know. I just I just never really got to it. But Do the Right Thing is a wild one, man.
+00:28:39 Jordan: Yeah.
+00:28:40 Darius: I was going to ask, have you seen Kirkland? We reviewed that one.
+00:28:42 Jordan: Yeah, but so part of why I haven't watched Do the Right Thing is because I've heard like it's mostly jarring and, you know, all that. And I think I just like was avoiding it, honestly. So eventually one day I'll just like suck it up and just, you know, and watch it. I know it's going to be great because I love Spike Lee, but I just heard it's very like emotionally stirring. And I was like, do I want to deal with that right now? And I haven't been wanting to deal with that.
+00:29:06 Darius: One all right um quick little aside I have the IDMB top 250 up I'm gonna go down the list and you tell me the first one you haven't seen um okay all right so we're gonna go with get it off the screen here Shawshank Redemption that's clearly number one Godfather one yep God or The Dark Knight yep of course uh Godfather 2 yep Lord of the Rings Return of the King no we're at #5. That's my, that would be my fifth. That would be my breaking point.
+00:29:39 Jordan: Yeah, that was the second one, I think.
+00:29:42 Darius: Let's just see if we can keep going. We won't go too long. 12 Angry Men we reviewed. So Schindler's List.
+00:29:50 Jordan: Oh, you know what? I have not seen that.
+00:29:51 Darius: Me either. So both five and seven for us. All right. That was not as interesting as I thought it would be. But there you have it, people. We now we have a list of movies that we need to review. Although some of those were three hours long. They don't make a lot of movies.
+00:30:06 Jordan: But that is fair.
+00:30:07 Darius: So moving into the next topic, Spider-Man, have you seen it? Well, you have seen it. How was it?
+00:30:14 Jordan: Yes, I saw it twice. I saw it Thursday night and then I saw it Saturday. I liked it. was really, really fun. It was like Any like big ******** Spider-Man fan will tell you they need we want to see Peter Parker down bad. We want to see him suffering and at wit's end and borderline with no will to live because that's when the movies are the best. And he kind of hits that point in this movie. It's definitely my favorite of the Tom Holland movies for sure. I got a little bit like he's been playing a character for 10 years, but it got a little bit annoying seeing him still like being like a I was</t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:00 Darius: You know what Rush Talk is, right?
+00:00:02 Jordan: No, what's that?
+00:00:03 Darius: Oh, it's like fraternity. Yeah. Sorority.
+00:00:05 Jordan: Yeah. Okay. Yeah.
+00:00:06 Darius: SEC sororities like doing dance routines. Yeah. And like they did some sorority, all white for sure, dancing to Not Like Us.
+00:00:16 Jordan: Oh, yes. I just saw that today. Yeah.
+00:00:18 Darius: And the people in the comments were doing what they do. And I'm like, how are you going to gatekeep a song performed at the ******* Super Bowl? Do you even hear yourself? Welcome to Out the Trunk with Jordan and Darius. My name is Darius. That's D's all up in your area on all socials.
+00:00:33 Jordan: And I'm Jordan. That's Jordan B. Riding on all socials.
+00:00:36 Darius: It's a podcast where two friends started talking in a bar and never stopped. This is our What's On Our Mind segment. We let you guys know what's on our mind. Quick hits, deeper questions, whatever we've seen on the internet. So Opening salvo, if you will. Did you see the graphic that I sent you on the run test, rundown?
+00:00:58 Jordan: Yeah, was it cozy movie night?
+00:01:00 Darius: Yeah, so we put it on the screen for the audience to follow along with. You got 15 bucks. What kind of night are you building?
+00:01:08 Jordan: 15 bucks. I'm going spending 5 bucks on Good Villas. It's a solid like 2 1/2, close to 3 hour movie. So that get more bang out of your buck.
+00:01:19 Darius: It's the only good movie up there. But yes.
+00:01:21 Jordan: That's fair. That's fair. I do like Clueless and Titanic though as a 90s kid. I'm also then I'm going to go nachos and cheese for my snack for my first snack. It's 9 bucks. Then I'm going to do Sour Patch Kid. That's one of my go-to puts me at 12 followed by I guess I'll do soda and I guess I'm pretty high nature, so I really just need a pillow, honestly. So I don't really need a blanket to watch a movie.
+00:01:51 Darius: Do we have to pick one from every line? I guess.
+00:01:54 Jordan: I mean, no, that's just.
+00:01:55 Darius: I think that's how it works because 5, 9, 12, 14, 15. Okay, so I'll play along. All right, so Goodfellas for sure. It's the only movie that I could actually watch out of those four. Popcorn for sure. I have a beef with movie theater nachos. It's not nachos, it's chips and cheese. If you went to any restaurant and ordered nachos and they brought you chips and cheese, you would be like, that's not nachos.
+00:02:23 Jordan: Unless you go to a good move theater, because mine has the real nachos with all the trimmings and stuff.
+00:02:29 Darius: I have another rant about people who need meals in the movie theater. That's just greedy.
+00:02:37 Jordan: One man's greedy is another man's multitasking.
+00:02:39 Darius: Fair enough, fair enough. Number 3, gonna go with some Sour Patch Kids. Actually, peanut M&amp;M's is tough, but I like those two.
+00:02:53 Jordan: I'm not opposed to snow caps either.
+00:02:55 Darius: Yeah, I like to do popcorn with the chocolate snacks. So you're going to go with the peanut M&amp;M's there. The $2 line, honestly, I just would rather just spend 13 bucks. I'm not lighting a candle. I don't even own slippers. I guess a pillow and the $1 line. We're going to do a soda. But the wine is intriguing. Maybe if I'm in the company of a young lady, wine would be on the menu. But if it's a solo dolo evening soda, I don't even like hot chocolate. It's literally just a melted Hershey bar and tea is not big on tea. So. So you want to talk about some bad movies you'll defend?
+00:03:40 Jordan: Yeah, I feel like, like before, like social media, you didn't really know what people viewed as bad in terms of like on a mass scale. So like I'm learning there's all these movies that people thought suck that I loved. So like, I'm my whole lot thing. These are great movies. People like all the it's universally panned. I'm like, Oh, **** I had no idea. So I made a list of movies that quote unquote are bad that I love and will defend to the death. One of them, that awkward moment with Zac Efron, Michael B Jordan, and Miles Teller. It's like a cheesy like guy rom-com, but I like rom-coms that like treat men as human beings. You know, they're not just a prop for who **** ** and then, you know, they give them flowers to the end and you're supposed to like them again.
+00:04:22 Darius: That's not considered a good movie.
+00:04:25 Jordan: Yeah, people hate that. Apparently it's considered a bad movie. Yeah.
+00:04:27 Darius: It's on our schedule to be reviewed. So I love that movie.
+00:04:33 Jordan: That's one of my cover movies. I've watched that movie probably like 7 * a year. So now what? Seven's extreme. Probably like 4 or 5 * a year. He's just not that into you. It's a like a one of those big ensemble rom-coms with like every actor in it. Like Jennifer Aniston's in it, Ben Affleck's in it. Who else? Bradley Cooper, Scarlet Johansen. It's like every white actor pretty much in it that was popular at that time period. Love that movie. X-Men Last Stand is the third one in the original trilogy. I didn't know people didn't like that movie. I was like, I learned it like last week. I was like, oh, **** I love that movie. Yeah, it's a good one of my favorite early Marvel movies. This one's that next two are also Marvel movies that were considered not great, I guess. Spider-Man 3, the black suit Spider-Man. People shoot on that movie. I'm like, first of all, any movie that involves Peter Parker getting it back in blood behind Uncle Ben, I'm in support of. We got that iconic dance scene where he's wearing the black suit and he's clapping outside the store. I always love that movie just for that scene alone. Billie McGuire. Because he spends the whole trailer just getting **** on by life. And for once, he like, you know, Stop taking the high roads. I love that. Then I'm going Daredevil, the Ben Affleck version. That was like widely panned. And I still don't know why. I love that movie. I got Michael Clark Duncan, rest in peace, playing Kingpin. He was a great super villain. Jennifer Garner was Electra. She looked fantastic. And she was nice with the sis. I think that's what they're called. Colin Farrell playing Bullseye. That was a fun choice. I don't know. I love the movie. Maybe it's because I was a kid when it came out. But yeah, I don't I don't get why certain people and I guess up your opinion, whatever. But those are movies that people **** on that I will always love.
+00:06:28 Darius: Okay. So I do understand what you mean because it's happened to me a lot more with like rap albums where you it's like you you lived your whole like my first, I don't know, 25 years for local. And then I looked on the internet and I was exposed to the world and I was like, wait, that didn't bang to y'all?
+00:06:48 Jordan: Yeah, no, like that's bad. That was bad.
+00:06:52 Darius: Number one with a bullet state property. You're not, I would defend that movie until the absolute end of my days. I ******* love that movie front to back. Watch it all the time.
+00:07:03 Jordan: Yeah.
+00:07:04 Darius: I mean, it doesn't, fit the theme in the sense that I kind of knew it was bad when I was watching it. Right.
+00:07:10 Jordan: You know you're bad. It's yeah. It's like Peyton Fool is bad, but you love it.
+00:07:15 Darius: One that actually does fit the theme, Mortal Kombat 1 and Annihilation. Like I watched those as a kid. The 90 ones, the new ones suck, but like the 1995 and 96 ones.
+00:07:27 Jordan: Yeah. Love the guy that just passed, right?
+00:07:29 Darius: Yeah.
+00:07:30 Jordan: Okay. Yeah.
+00:07:31 Darius: Love them. Did not know they weren't critically acclaimed, but they went, they won Oscars in my house. A Lot Like Love is my favorite rom-com of all time. I'm pretty much the only human being who holds that position.
+00:07:43 Jordan: Yeah, you do. You do love that movie.
+00:07:45 Darius: Why Did I Get Married? One is, like most Salad Perry movies, it's not really that blue, critically acclaimed movie, but I love it. It's the only one of his movies that I can rewatch. Correct. To get serious out the furnace with Christian Bale and Casey Affleck, Woody Harrelson.
+00:08:05 Jordan: So we saw Donna, I think is in it, right?
+00:08:07 Darius: Maybe. I don't recall any women in that movie other than Christian Bale, like a woman or wife or whatever.
+00:08:14 Jordan: Yeah, I love that movie.
+00:08:15 Darius: Woody Harrelson plays like a borderline supernatural. Yeah, monster character. It's great. I didn't. Yeah, because like it came out with I live in California and I just went and watched it and, you know, I didn't know that it had received mixed reviews, but I love that movie. And we reviewed this one. You're next. The horror movie. Yeah. It's I know that movie's bad, but I do enjoy that movie.
+00:08:40 Jordan: It's so bad. It's funny.
+00:08:42 Darius: Correct.
+00:08:44 Jordan: Yeah, I'm at that.
+00:08:45 Darius: One quick album. I did not know this wasn't like universally regarded as a classic. Jada kisses kiss the game. Goodbye. Literally was like no skips. Adored that album. And the Internet is kind of lukewarm about it. And so I hear all the time that Jaded Kiss is like the best rapper without a classic. And I'm like, yeah, that's I count like two or three of them, but kiss the gun.
+00:09:07 Jordan: Okay. So I got two albums for that. I like that. For me, it's considered like culture shifting now. By the time people **** on that movie album, it awaits in heartbreak. I love that album. And then Yeezus, people **** on Yeezus. I love that album too. There's some good music on there. Also, I think it's like, if you only listen to rap music, that wasn't the album for you. know, that was for people who listen to other genres and have different flavors to their playlists, so to speak. I thought of another movie that's really bad, but I ******* love. It's a movie called Homefront. It's got Jason Statham and James Franco. Jason Statham plays like, well, he plays himself. He does in every movie where he's like, he's like a retired, like agent or undercover agent and he has a kid who there, her mom just died and they moved to this Podong town and she goes to school and she gets bullied by this big fat kid, but because her dad's an agent, she can fight it. So the kid's like being a bully. So she knocks the kid out. The parents come to school and cause a scene and the dad tries to fight Jason Statham. You know how that goes. But of course, the dad's wife has like, meth dealer brother who's James Franco, who's like some evil villain or whatever. And it's just like a dope *** like shoot him up, bang, bang movie.
+00:10:23 Darius: I'm convinced Jason Tatum, Statum doesn't actually read the scripts. He just shows up and films like 10 hours and they just chop it up into four movies. He doesn't, he's like, I'm doing the same thing in every scene.
+00:10:34 Jordan: Him in the rock, yeah.
+00:10:36 Darius: One 10 hour day and then you make 4 movies out of this.
+00:10:39 Jordan: That's it. That's it. That's all they do.
+00:10:42 Darius: Similar vein. Olympus has fallen and London has fallen. The CGI is God awful. The plot makes no sense.
+00:10:50 Jordan: Not at all.
+00:10:51 Darius: And you know, I can't, I watch up until, I watch about an hour, then I have to shut them off because they get stupid. But like the first hour, both of those movies are, they went triple platinum in my home. If you, Okay, I'm not mad at that. That's what the kids say.
+00:11:07 Jordan: So that was like, yeah, that was the time of your period where like, They kept making movies that were just clones of each other and dropping them the same year. I remember it was Olympus Down and then there was the Jamie Foxx version with Shannon Tatum.
+00:11:20 Darius: White House Down. White Hawk or something. Yeah. I'm not sure. This might just be an internet rumor, but I think it was literally the same script sold twice to two different studios.
+00:11:34 Jordan: I believe it.
+00:11:35 Darius: Actually, I think I heard that.
+00:11:37 Jordan: I think I heard that. Yeah, I think I did hear that.
+00:11:38 Darius: Because of some legal wrangling, they both got to make it and they just was like, yeah, you go six months first on this one. I'll go six months first.
+00:11:48 Jordan: This was like after Black Swan came out. And I think Mila Kunis and Natalie Portman were like pretty good friends too. So I think they knew they were just like making the same movies like separately. Yeah.
+00:11:57 Darius: Don't quote me on it, but I think it's actually literally like the same script.
+00:12:01 Jordan: I think that did happen. I think I remember seeing that on like Twitter like a decade ago.
+00:12:06 Darius: But I'm pretty sure. Yeah, man, Olympus is following the idea that like an enemy fighter jet could get all the way to the White House.
+00:12:14 Jordan: And no one know anything.
+00:12:16 Darius: And no one, no one on the radar, no one called, no one had been gone.
+00:12:20 Jordan: Not even a little bit.
+00:12:21 Darius: Wait till it was 10 minutes away. But you know, so I think it's.
+00:12:26 Jordan: And of course it's always an inside job.
+00:12:28 Darius: Yeah, of course. I mean, of course. And then, yeah, I was going to say something like you knew who it was when you were watching it, but I think it's. It's good to have a healthy balance. Like we make the joke all the time. Like we, I'm not sitting and watching Citizen Kane every day. Like, you know, you have to have, it's like a critic's job is what a critic's job is. And don't get me wrong. Like I want them to be snobby. That's literally the job. But like, right.
+00:12:55 Jordan: The fan doesn't necessarily.
+00:12:57 Darius: And we're consumers and you know, like I don't always want a dialogue driven, you know, character study when that, you know, on a Tuesday night to get off of work.
+00:13:08 Jordan: Nope.
+00:13:08 Darius: you just like it's different moods for different things. Sometimes I want the Migos and sometimes I want nots and like that's the same thing with the movies, so. Correct, 100%. So you want to get into the next one?
+00:13:23 Jordan: Yeah, what's the next topic?
+00:13:25 Darius: So I found us a generic prompt to get us yapping. So just straight up, just going to throw it out there generic for you. What's something that gets better with age and what's something that gets worse with age?
+00:13:38 Jordan: Something that gets better with age, I'd say perspective. Okay. That's the first thing I thought of that gets better with age. You look back and it's like, the **** that you thought meant so much or was gonna mean so much to the person you thought was gonna mean so much, it was just like a small part of your journey, you know? Or even just like **** that you spassed out about, you just spassed out about now you're like, what am I doing? Like, what was I thinking? Like, why am I? Raising my blood pressure over that for, like, come on, man. I think things also get better with aged wine, of course. I'd say it. I had to get it too obvious to not say it. I'd say art, you know, good art, age as well, and it's timeless. Collectibles items, you know, like mint, trading cards, comic books, the little action figures you don't open, that sort of thing. I'd say high value. No, I'm just kidding. No, I think that's what I got for things to get better. I mean, I'm sure I could think of something else if I really had time to sit down. But things get worse with age, back pain, knee pain. I almost exempted physical pain. Alcohol tolerance.
+00:14:49 Darius: Oh, man. Oh, dude. Yeah, like that's the thing is just the way your body responds to booze just changes. I'd say about 30 to 33 is when I was just like, you know, the the the Wednesday bad day at work. Let me get a couple of beers and a burger at the bar that just had to stop because I got just my whole week and my rest of the week would be shot. And so, yeah, that's something that definitely changes. But The so yeah, gym recovery is definitely on the worst list. But the better list, I think patience, I, I can't remember the last time I like just like, like yelled just because I was a kid, you know, you're young and testosterone surging and like, you don't you just you just everything is makes you angry. And like, I don't. Yeah, very little actually gets me like, like, like just steam coming out of my ears, angry mental clarity, just like decision making discipline. Like I can if I'm given a task and it's due in three weeks, I can map that out in a way that I just wasn't capable of ten years ago.
+00:16:06 Jordan: Yeah.
+00:16:07 Darius: And just day to day things. One thing I had on here better is food noise is what I call like a lot of people who are on GLP ones, they'll say like the biggest thing is like quieting food noise. They don't think about food. And I'm not on a GLP one, which obviously you could look at me and tell, but like just like you don't you don't like. Yeah, I don't know. Like I just don't like I used to constantly think about food and now I just kind of like I make most of my meals on Sunday for the rest of the week. And that helps because like you just know what you're going to eat. And, you know, I indulge here and there, don't get me wrong, but like I've definitely noticed that like food noise goes down as I've gotten older. Yeah, long term decision making. When I was, you know, when I was in my early to mid twenties, I spent every dollar I had and now like money doesn't burn a hole in my pocket like it used to. And it's just easier to map things out and just, you know, make this long term thinking and decision making gets easier. Worse sleep. It's like I used to be able to hit my head on the pillow and just be out for 9 hours and it'd be fine. But now it's like, you know, part of that is YouTube shorts. I mean, watching videos of people cleaning carpets, right? I think this is it's going to sound counterintuitive, but gets worse with age is your tolerance for risk in a sense that like I do think some risk taking behavior is good and you sort of lose your stomach for that as you get out. And there's a reason why Most billion dollar companies are founded by people in their late twenties, early thirties, and it's because they just have a stomach for risk and chance that older people don't. And like, yeah, I do think some risk taking is good. You got anything else?
+00:17:57 Jordan: Things have gotten better. Yeah, I'd say like I'm I'm I've gotten better at planning or and getting and I'm getting better at planning things out as I age. Man, I still, I've always kind of dealt with like executive dysfunction. Like it just, and I'm gonna start to overwhelm you like, **** that, I'll just deal with it later, deal with it when I have to deal with it. Which of course just, you know, everything piles up, it all hits at one time, you know, that's kind of like what a lot of my 20s and first one or two years in my 30s was like, you know. So definitely trying to be more proactive with that. And also like life is going to force you to eventually. So you might as well get a head start while you before things get too catastrophic. I'd say probably acceptance. I think something I've gotten better at as I've aged. Like I have a way shorter not tolerance, but I'll say I have a way shorter lease for certain things like with other people and with myself. Before dealing with someone, friend, whatever, relationship, whatever, I've noticed things and I'd be like, well, and I just kind of kick it down the road or keep on keeping on in the relationship. And then last few years as I've gotten older, I'm like, wait, I don't have to wait for it to get worst case scenario. I don't have to wait for it to get as bad as it possibly can get. I don't have to wait until they stab me in the back to cut them off. You know what I mean? Like, the second I think they'd have a knife, I should just cut them off, you know? The second I see them do it to somebody else or whatever, or the second I see them, you know, some sort of big character flaw, whatever the case may be, that's enough of a reason to end, or at least to separate, create distance, you know? I feel like a lot of times we, as humans, we try to give people the benefit of the doubt and like, or people like this whole thing was like, you know, I've been building a Rico in my head over like So when I cut them off, I had no regrets. But for the most part, looking back, whenever I've cut people off, I didn't have any regrets. I've only ever regretted keeping people around, you know, so just getting better at and not feeling like I'm losing something by losing a person.
+00:20:04 Darius: Yeah.
+00:20:04 Jordan: You know, like you can grieve the relationship, but like, you're still you and you still have value. So you losing them is not actually a loss, you know?
+00:20:11 Darius: It's just your discernment gets better, right? You can, you can, it's easier to determine who means well and who means not so well, you know, and that that reveals itself earlier in the interaction and you're less clouded by, you know, the the door endorphins that come with meeting someone new, whether that be a new friend or a new girlfriend or whatever. Right. Which is which which category would you put dating in? Does that get better or worse with age?
+00:20:40 Jordan: Oh, that's hard to say. It's almost like it's almost like to like putting NBA terms almost like a plus minus like some games because some games is bad like like it's you know because it's like you get better with discernment but then because your discernment is better your tolerance is lower yeah so because your tolerance is lower your options are you know or in the same token it's also like things that you maybe you don't necessarily want to deal with be it various like circumstances. I'll let you kind of figure that out from there because I don't want to disparage anyone on camera. Fair enough.
+00:21:25 Darius: I think it's unequivocally better. I would not trade my dating life at 38 for my dating life at 28. It's not even close. It is. It's a lot less chaotic, which can be plus or minus, but.
+00:21:40 Jordan: Right.
+00:21:43 Darius: Yeah, it's not even close. That was a bit of a mess in my late 20s. So I do think it gets better. Ideally, you wouldn't be dating at all in your late 30s. You have a family, but you know, here we are. But given the circumstances that I found myself in, I would say that it is better for sure.
+00:22:04 Jordan: Got you.
+00:22:05 Darius: Want to get into the next or you got another?
+00:22:07 Jordan: Yes, follow up. When you said you were a mess, what do you mean by that?
+00:22:11 Darius: I just was chaotic, right? I just, you know, juggling, lying.
+00:22:19 Jordan: Yeah.
+00:22:20 Darius: Just, you know, a typical bachelor shenanigans. Yeah. You know, I. Yeah, it just it depends on who you ask, but I think some experiences were better than others, but. I just wasn't. My discernment was worse and I just wasn't good as good at making decisions.
+00:22:43 Jordan: Yeah, for sure. I've definitely been there. Like I look back at certain things and I'm like, I could have totally avoided that if I listened to my gut in the first two weeks and not tried to benefit the doubt my way out of reality, you know?
+00:23:00 Darius: I got you, man. Two Americas.
+00:23:04 Jordan: Oh, yeah. So You saw the clip I sent you.
+00:23:07 Darius: Yeah, that was Foxworth.
+00:23:09 Jordan: Yeah, where he was on, was it Jeopardy or some sort of game show?
+00:23:12 Darius: And he was like, ESPN Jeopardy or something.
+00:23:14 Jordan: Cause Joe Fox was like, yeah, I was like, what is he doing? And he was like, you know, my favorite thing is watching game shows when they asked white people black history questions or questions about black culture, because they never knew any of it. And it brought to mind, I actually was at a trivia night at the spot one time and they, a lot of the shows were, obviously and references were, mostly white. And then there was like a section where they were asking like black stuff. I was like, thank God I can get some points. And then it was just me and Daniel rattling them off.
+00:23:51 Darius: It's funny. Like, as soon as it panned Dominique, I was going to say, bye. I just knew he's going to tell some bad comic view joke. And of course he did.
+00:23:58 Jordan: Yeah.
+00:24:00 Darius: White people do this. Black people do that. Black people do this. I just know it. I just knew it. No, it's definitely true because I've definitely been at trivia nights and it went to like the music section and like. I was able to answer certain questions and other people were able to answer other questions. And like, these people didn't even know that Marvin Gaye's dad killed him. It was like, the question was like, this soul singer died in 1983, you know, because his father shot him. And I was like, it's Marvin Gaye. And like, I did an impromptu history lesson, I guess, played a little as collective. But Yeah. Normally I find those jokes just cheesy because I knew he was going to do it, but that was pretty good. That was pretty funny.
+00:24:41 Jordan: Oh, no, yeah, for sure.
+00:24:42 Darius: My favorite Jeopardy stuff is when they do sports section and those nerds have no idea. Oh, yeah, Because yeah, they that's just they always straight brick every sports column and it's funny to me.
+00:24:58 Jordan: It also just made me think of like different things where like, just like that are actual real cultural differences. Like, you know, when we've been at sports bars and we've seen, we've seen black men wear like hats, right? And then a white person been like, oh, is that your team? Or how long have you been a team of that team? Or how did you become a fan of that team if you're in North Carolina? And that's a Yankees hat or whatever. And it's like, we just, we like hats. That's it.
+00:25:22 Darius: That's it. That's a good one. I just lost my train of thought. Yeah, it is. I mean, look, it's becoming less culturally salient as you know, we just become one bigger melting pot and people, you know, aren't, you know, it's just the internet has collapsed a lot of the context barriers and you just people can peek into our world and we can peek into their world. I saw something earlier. You know what Rush Talk is, right?
+00:25:56 Jordan: No, what's that?
+00:25:57 Darius: It's like fraternity. Yeah. Sorority.
+00:25:59 Jordan: Okay. Yeah.
+00:26:00 Darius: SEC sororities like doing dance routines to and like they did some sorority all white for sure dancing to not like us.
+00:26:10 Jordan: Oh, yes. I just saw that today. Yeah.
+00:26:12 Darius: And the people in the comments were doing what they do. And I'm like, how are you going to gatekeep a song performed at the ******* Super Bowl? Do you even hear yourself? How you gonna gatekeep a song performed at the Super Bowl? Explain to me how that makes sense.
+00:26:31 Jordan: That's a good point. That's a good point. I think they're more so talking about because it literally is the antithesis of the sentiment of the song. But you're not wrong.
+00:26:39 Darius: You performed it in front of 100 million people. The vast majority of them are white. You cannot gatekeep a song performed at the Super Bowl. It's just these people kill me, man. It's like they when they complain about like how woke has changed and it's like, y'all cannot be this fragile. Like you just, you just cannot possibly be this fragile. Okay, so our people are stronger than this.
+00:26:59 Jordan: We are stronger than this. But okay, so when you say how woke has changed, what do you what do you mean? Do you mean how they use it as the new N-word?
+00:27:04 Darius: Because that is not the new N-word. It's just there was a culture.
+00:27:07 Jordan: Some people do use that.
+00:27:08 Darius: There was a culture of annoying *** people in 2020 who did stupid land acknowledgements and other **** ****. And all of that is. No, that's fine.
+00:27:22 Jordan: No, that's fine. I'm talking about like the far, far left. I'm sorry, the far, far right. When they there's a segment they use it like that.
+00:27:31 Darius: My thing is, if you use a term on a Twitter account with 30,000 followers unlocked.
+00:27:35 Jordan: We're going to see it. Yeah, right.
+00:27:37 Darius: You're not gatekeeping. You have 30,000 followers. You thought they weren't listening to you. Like you want to influence, but then you're mad when people are influenced. Make up. What do you want? I just, like.
+00:27:55 Jordan: That's valid.
+00:27:56 Darius: So that's the person who wrote the song decided to perform it at the Super Bowl. Clearly he don't care about gatekeeping it. He's not.
+00:28:02 Jordan: Yeah, he was not gatekeeping. He was not gatekeeping.
+00:28:05 Darius: So it's not for us.
+00:28:06 Jordan: He wanted everyone to know what he thought of Drake.
+00:28:09 Darius: It's not for us anymore. Once you do something at the Super Bowl, it's not for us anymore.
+00:28:13 Jordan: That's true. That's true. Yeah. You can't be like, oh, they did dance to Dirty Diane or some ****. Like it's, you know, gatekeeper. Yeah, right.
+00:28:22 Darius: ******* 80 million records, man.
+00:28:24 Jordan: The whites are gonna hear Purple Rain, guys.
+00:28:26 Darius: It's just like, mathematically speaking, if you want any rapper to like pop, the vast majority of their fan base is gonna be white people because there's just, we're only like 14% of the population. You can't, a rapper cannot do an arena show It's math. Like it's just not possible. So you either have to pick if you want these people to be big and huge and do arenas and Super Bowls, their fan base is going to be primarily white. That's just the math. I'm sorry.
+00:28:54 Jordan: Yeah. I got to say for example. So I remember in high school we were reading Their Eyes Are Watching God. Did you read that book?
+00:29:07 Darius: No, maybe if I did, I don't remember any of it. So let's just go with no.
+00:29:13 Jordan: Okay, so it's a book, you know, set in the South. I can't remember which era, but either around Jim Crow or during slavery, shortly after. I can't remember the exact period. And so the dialect and it had all the apostrophes and it was talking how they spoke back then and how we speak when we're the families and **** like that, whatever. I remember our teacher was like, this guy's book is really challenging. It's going to be really hard to read. The dialect is very difficult. You know, he almost acted like it was another language. And I'm reading it and I'm like, this is a raising in the sign. Like, this is simple ****. This is how we talk at Thanksgiving. And but like hearing like my classmates and my teachers like read it out loud was hysterical. Like it was it was like if you ever taken like a foreign language class and like that one kid who just can't verbalize it.
+00:29:59 Darius: Yeah.
+00:30:01 Jordan: It was like that.
+00:30:03 Darius: I will. I would argue it'd be worse if they were really comfortable saying those words.
+00:30:08 Jordan: Yeah.
+00:30:10 Darius: They're like, I got this right here.
+00:30:12 Jordan: And they were like, all right, hold up, y'all. I was be cooking.
+00:30:16 Darius: He was like, my dad says this stuff all the time. I go, I know the words.
+00:30:23 Jordan: You know, our maid talks like that.
+00:30:29 Darius: Yeah, it's I would he was it is definitely a funny cultural difference, but it is good that your teacher was aware enough to know that he should give a little bit of a warning there. You got any more examples?
+00:30:47 Jordan: Trying to think. You know, I'd say that the concept of like a stay at home mom, that's kind of a cultural thing, it seems like, you know, like just historically. I remember I was in high school when I learned people that existed in real life, like in this day and age. I thought that was just like some Leave it to Beaver ****. I didn't think people actually did that in real life anymore, because often women in my family worked. So like in high school, I remember we did like a survey. It was like, who had a stay-at-home mom? And like a lot of the kids' moms were stay-at-home moms. And I was like, wait, what? Like I had no idea. My mom worked, all my cousin's moms worked, you know, my friend's moms worked. That to me was like mind-blowing.
+00:31:26 Darius: I think there's more of a sign of affluence. more, more like white people in the aggregate are more fluent than black people. And as black people got more affluent, like I know a couple black stay at home moms now and it's because their husbands have money and you know, what she would make is, is less than the daycare. And so, right, y</t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:00 Jordan
+Drake and Josh, the show, Drake.
+00:00:04 Darius
+What is Drake and Josh?
+00:00:06 Jordan
+You never seen Drake and Josh? Are you serious?
+00:00:09 Darius
+What is it?
+00:00:10 Jordan
+No, the Nickelodeon. Are you kidding, right? Drake? Remember we talked about him coming to Raleigh for like a bar fest or something like that? He was hosting.
+00:00:17 Darius
+You watched that show?
+00:00:19 Jordan
+Yeah, I was a teenager when that show came out.
+00:00:21 Darius
+But you're black.
+00:00:23 Jordan
+Yeah. For like 30 plus years. Yeah.
+00:00:27 Darius
+You watch that. You watch that show.
+00:00:30 Jordan
+Yeah, I watched that show. Nickelodeon had slaps back in the day. I don't care. You didn't watch the white show. You didn't watch the white show. Yes, yeah.
+00:00:41 Darius
+You didn't watch the white show.
+00:00:42 Jordan
+You didn't watch the show. I guess I watched the show. You didn't watch that show when you were older. So you were older. You were probably like 20 when that show came out.
+00:00:52 Darius
+I did. I stopped watching. All manner of cartoon when I went through puberty, because that's when I met girls. I do still play pokémon on Nintendo Switch.
+00:01:04 Jordan
+Okay, so that's 10 times worse. That is 10 times worse than watching Drake and Josh as a teenager.
+00:01:10 Darius
+It is not one. Welcome to Out the Trunk with Jordan and Darius, the podcast where two people started talking at a bar and never stopped. My name is Darius. That's Deez. I love the area on all socials.
+00:01:24 Jordan
+And I'm Jordan that's going to be writing on all socials.
+00:01:26 Darius
+This is our What's On Our Mind segment where we let you guys know what's on our mind. Quick, quick hits, deeper questions, things that we have seen on the internet. And going to date the episode a little bit, but Madden 27 just came out. Did you pick it up?
+00:01:40 Jordan
+Yeah, I got it on digital. I actually was playing it for a little bit before we got on here.
+00:01:46 Darius
+Do they even still sell physical copies of video games anywhere?
+00:01:51 Jordan
+I mean, I still get them for Christmas sometimes, so fair enough. But if I can get the, if I get the digital, if I buy it now, it's usually just digital.
+00:02:01 Darius
+Okay, you like it.
+00:02:04 Jordan
+I'm still getting used to it, to be honest. I got the catch timer thing off that makes offense much more fun. I'm still figuring out the audible zone defense because I'm just been like faking cover to nonstop.
+00:02:16 Darius
+So what do you what modes do you play in?
+00:02:23 Jordan
+I play all Madden, all Madden and competitive mode or arcade mode. I'll talk between those two.
+00:02:28 Darius
+No, do you play like exhibition games, franchise mode online?
+00:02:32 Jordan
+Oh, okay. I do a lot of exhibition games. Not a big franchise guy. Well, I'll do like superstar where I'll create a quarterback and go through the career. I'll do that. I'm not really. I don't really do franchise mode A lot. I might get back into playing online, though, since it seems like we're all having trouble with the CPU. So maybe that may make life a little bit easier.
+00:02:55 Darius
+How is this your first Madden in a few years?
+00:02:58 Jordan
+No, I get it pretty much every year.
+00:03:00 Darius
+Were you good at the last year?
+00:03:02 Jordan
+Yeah, that's what's so frustrating about this year.
+00:03:05 Darius
+Yeah, I mean, I don't think the gameplay is a little different. They've moved some buttons around, but it's definitely they've made it so you kind of have to understand football a little bit. But I play on all pro. I play franchise mode and I love it, man. Yeah, you know, I lose sometimes and I'm rebuilding the Jets and drafted Dante more out of Oregon and.
+00:03:30 Jordan
+Okay.
+00:03:31 Darius
+Greener pastures, man. I just like managing the team. So the free agency, the draft picks, the.
+00:03:35 Jordan
+Transactions and all that.
+00:03:37 Darius
+I mean, I play the games too, but that's kind of more into that part of it, running the team than like I can't, I couldn't just do exhibition because it's just, they're just isolated and like I never get attached to anything. It's just, you're just running isolated. I mean, I'm going to get back into online multiplayer this year, but yeah, that's mostly what I buy it for is offline franchise mode. Occasionally, every few years we'll do an online franchise mode with people I know, but for the most part, it's just offline franchise mode.
+00:04:09 Jordan
+Oh yeah, I'm totally opposite. I'd rather play. I'd rather just play like I'll, you know, any kind of games really. I love the drills, skill trainer, all that stuff, the offense only stuff. Yeah, and also I think I just myself play whatever. I like doing calling a bunch of audibles, so we making switches. doing things at the line of scrimmage, moving corners, safeties, all that stuff. So I got to figure this out. But I also took like a week off from playing it. I've been playing a lot of NHL 2026 lately too. So I've been toddling between those two games. It's fun. I really like it. I go on that one. I've been playing mostly rookie mode, but I do play semi-pro occasionally. It's just that the stick maneuvers I'm still trying to figure out because I don't know what the words are. So I don't know how to find the controls. to use the words to make the moves. But breaking down the schematics and stuff and reacting in real time is pretty fun. Breaking down defenses and stuff like that.
+00:05:04 Darius
+Who do you play with?
+00:05:06 Jordan
+The Canes.
+00:05:07 Darius
+Okay.
+00:05:07 Jordan
+So only team I know really, really well. because I play against other teams, like I'm learning those teams now too.
+00:05:13 Darius
+Yeah.
+00:05:14 Jordan
+New Jersey, really, really good. The Canadians, really good defense. It's like they're playing a different speed. Yeah, so it's fun getting to learn the game that way too.
+00:05:23 Darius
+What, just playing exhibition games?
+00:05:27 Jordan
+Yeah, mostly. pretty much mostly exhibition games. I don't know if I'm good enough to play online yet. I'm not about to get my head beat in by some 12 year olds.
+00:05:35 Darius
+Yeah, I wouldn't even know how to play the hockey franchise mode, but I could I mean, I could play the exhibitions. You guys outside of sports, you playing any other games?
+00:05:46 Jordan
+Yeah, I was playing the Bond game. I was like hooked on that for a long time. I'm like 75 to 80% done with that game. I took a break because I got stuck and I just, I literally don't know what to do. There's like no clues or hints. I'm just in this office building looking for a command center. It's like 60 floors. I'm just like, all right guys, you got it.
+00:06:08 Darius
+Have you tried throwing it into like a ChatGPT?
+00:06:13 Jordan
+No, I'd usually do YouTube.
+00:06:16 Darius
+Yeah, the videos, they just take too long and the people talk too much.
+00:06:19 Jordan
+So I just, that's also true.
+00:06:21 Darius
+Throw my problem into an LLM and be like, how do I fix this? If I, man, you click a YouTube video and they spend 2 minutes prepping you to tell you what you need to do and I just, I can't take it.
+00:06:36 Jordan
+No, I hear you. I'll just skip through like thank God for the automatic chapters feature on YouTube because I'll just go right to the whatever it looks like where I'm at in the game.
+00:06:44 Darius
+You know, it's like if they're reading an ad, I get to get your money. I'm not mad about ads. But like the two minutes of clearing your throat. How is this? Like, I know you played this back and it's not just cut it. Like, you're doing it for free.
+00:06:57 Jordan
+Like you're not getting money off this. I see your view numbers.
+00:07:01 Darius
+Just cut it. does. It should not take you 5 minutes to get to where we were trying to go. It's actually one of my biggest podcast listener pet peeves is when the host spends 90 seconds setting up a question. And it's just like, I don't even, by the time he gets it out, I don't even know what his question is anymore.
+00:07:20 Jordan
+I don't remember what I was looking up.
+00:07:21 Darius
+Right, It's just like, dude, just ask your question. Or they ask the question and answer it at the same time. I hate that. So right now I'm playing.
+00:07:32 Jordan
+Be for TikTok too.
+00:07:33 Darius
+Oh yeah, that's another one. Right now I am playing. I just be Resident Evil Requiem. Okay. A dude still hop back on the Mass Effect. When I Mass Effect two and three, when I get bored, I just got Mortal Kombat, the collection. It was on sale for like 25 or like 25 bucks. And oh yeah, full price, full price, 50, that's not worth it. But for 25, you get basically all the old Mortal Kombat games before, I don't know, 2000. And it's like a, it's more like, you know what Criterion does with Blu-rays? It's kind of like that. It's like the games are, it's like an anthology almost. You get archival footage of the original engineers talking and it's restored and the games are almost beside the point. It's like a collector. It's like a criterion version of what Mortal Kombat was to. Okay, that's kind of dope. I mean, it's cool. If it was 50, I would have never bought it. But for 25 on a Friday night, What the hell? That's like, I mean, that's a meal. It's a little bit more than a meal at Chick-fil-A. So whatever.
+00:08:49 Jordan
+Yeah, that's two combos.
+00:08:51 Darius
+You know, so that's what I'm into, man, is just Grand Theft Auto, the PS2 trilogy, three, Vice City is San Andreas remastered is on the PlayStation Network for 18 bucks. So I might pick that up.
+00:09:08 Jordan
+You know, is that I might cop that.
+00:09:11 Darius
+You know, I've just I've been going out a lot less lately and it's I've been finding rediscovering my love of playing video games. It's keeping me in the crib and it's a lot cheaper to stay in the house playing a video game. So it's like just buy a game and it's something to do on a Friday night. You get a new game and it's you don't get that. I don't at least I don't get that like hungry to go out. So it's kind of it's keeping me It's a cheap hobby. It's a cheap replacement for going out. So it's healthy.
+00:09:44 Jordan
+Yeah, that's true. You don't gain weight from playing video games.
+00:09:49 Darius
+Well, you absolutely can.
+00:09:53 Jordan
+Yeah, well, yeah, that's true. That's true.
+00:09:55 Darius
+All things considered, it is it is better for you than partying, but it can't be the only thing you ever do either.
+00:10:02 Jordan
+Yeah, you can't just. ghost your social life and you know, it's just balance.
+00:10:08 Darius
+But instead of spending all weekend, you know, being a degenerate, like I'll stay in Friday and go on Saturday. And so I still get to it's like the best of both worlds. And then I wake up Sunday feeling better and then by lifts on Monday are just way better. And so yeah, I think that's a so it's been like a month and so far I like it. So we'll see what happens with that going forward.
+00:10:30 Jordan
+Yeah, it's not a bad routine.
+00:10:32 Darius
+You got anything else for that one, man? Any video game talk you want to get off the chest right now?
+00:10:38 Jordan
+I have been going back to Spider-Man, Miles Morales, PS5 game. I've been playing that since Spider-Man Brainer Day has been out. I've been playing that a lot. That's fun. I first got that game, **** probably like 2023, maybe, 2022. But I'm in the plus mode where I beat the story. So now I'm just running around fighting people and swinging and flying all over New York. So that's fun.
+00:11:03 Darius
+That's the best, man. I have The Last of Us one and two. And once you beat it, you get the plus mode. And yeah, I mean, that's the second playthrough is always better because you get all the upgrades and you know what to do. And I've probably played The Last of Us to 200 hours, probably, you know? Yeah. And so it's just, once you have all the weapons and stuff, and I maintain that no game has more dynamic combat than that. So that's good stuff, man.
+00:11:32 Jordan
+Okay.
+00:11:33 Darius
+You know, shout out to us rediscovering a childhood hobby, you know?
+00:11:38 Jordan
+Yes, gaming is fun when you also like do what you're supposed to do in life. As long as you're like not quitting work and it's like.
+00:11:47 Darius
+Everything, most things are fine in moderation, you know? So yeah. It's just about balance. So you want to get into some TV show talk?
+00:11:57 Jordan
+Yeah, so we were talking last week about protagonists, what makes industry protagonists, and ones we love, kind of ones we hate. So I want to talk about shows that we love with protagonists or characters that we really truly hate. And also I think characters that just got way too much of a pass in the lore of the fans and stuff, So for my first one is Lily from How I Met Your Mother.
+00:12:24 Darius
+Okay.
+00:12:25 Jordan
+She, end of season one, she leaves her fiance, not at the altar, basically calls off the wedding to get a, she got a fellowship in San Francisco, which she applied for during the engagement, didn't tell him about. He found out through a voicemail type thing, As one does. Yeah. And she, and she, goes off to San Francisco, flames out and then comes back and expects him to just like be cool and take her back, whatever. They end up getting back together and they are a great love story. But I just always hated that. And then, she meddled in all their friends' relationships and did some manipulative stuff, she could be a bit annoying. So that's one. Another one is Drake and Josh, the show, Drake.
+00:13:15 Darius
+What is Drake and Josh?
+00:13:17 Jordan
+You've never seen Drake and Josh? Are you serious?
+00:13:19 Darius
+What is it?
+00:13:21 Jordan
+The Nickelodeon, are you kidding, right? Drake, remember we talked about him coming to Raleigh for like a bar fest or something like that? He was hosting.
+00:13:28 Darius
+You watched that show?
+00:13:30 Jordan
+Yeah, I was a teenager when that show came out.
+00:13:32 Darius
+But you're black.
+00:13:34 Jordan
+Yeah. For like 30 plus years. Yeah.
+00:13:38 Darius
+You watch that? You watch that show.
+00:13:40 Jordan
+Yeah, I watched that show. Nickelodeon had slaps back in the day. I don't care. You didn't watch the white show? Yes. Yeah.
+00:13:52 Darius
+You didn't watch the white show.
+00:13:54 Jordan
+I guess I watched the show. You didn't watch that show when you were older. So you were older. You were probably like.
+00:14:03 Darius
+I did. I stopped watching all manner of cartoon when I went through puberty. Cause that's when I met girls. No, you watch this.
+00:14:16 Jordan
+Yeah. You didn't watch that show at all. That's crazy. Frank and Josh is a great show.
+00:14:24 Darius
+Not to take a dark twist, but I was first made aware of this man during that Nickelodeon exposure. During the, and we'll go there, but that documentary. The first time I was made aware that person existed.
+00:14:37 Jordan
+That's crazy.
+00:14:38 Darius
+No, man, my Nickelodeon ended with like Rugrats and Rocco's Modern Life.
+00:14:42 Jordan
+And that's like when mine started.
+00:14:45 Darius
+I mean, I was out, man. Any sort of like pokémon, wrestling, all that stuff. I mean, I used like puberty colloquially because that's the only like time period I could think of where it changed. But like, I don't know where it switch flipped, but it was just like one day. I just put that **** down. Like I don't really.
+00:15:08 Jordan
+I mean, I pretty much, yeah, I thought I quit pokémon around like eight or nine, maybe 10. And then wrestling, I was, that was a phase from like I'll give you this confession.
+00:15:20 Darius
+I do still play pokémon on Nintendo Switch.
+00:15:23 Jordan
+Okay, so that's 10 times worse. That is 10 times worse than watching Drake and Josh as a teenager.
+00:15:29 Darius
+It is not.
+00:15:32 Jordan
+Hey, we're going to take a poll. That's going on social media.
+00:15:37 Darius
+It is not. But you know what? No, I do still play the last pokémon when I got my switch to I bought pokémon Shining Pearl and I'm probably like 150 hours into that.
+00:15:52 Jordan
+Okay.
+00:15:53 Darius
+And that was in May. So there I that is I think the only person who would know that would be our friend Tori. And that's because she plays.
+00:16:09 Jordan
+Oh yeah, she loves. Yeah, that's it. Yeah.
+00:16:11 Darius
+And so but that would be I guess that's my podcast confession is that I do. I do not watch, but I do still play pokémon. I'm going to get Scarlett here in a second. Well, not in football is about to start, so I don't really have time, but yeah. No, man, I've not. Why? I don't the Nickelodeon stuff. Yeah, I just the whole that whole when I'm watching that documentary, that whole era after like all that was just completely alien to me. I was watching it like it was a true crime documentary. It wasn't anything like nostalgia or anything like that.
+00:16:50 Jordan
+Oh, okay. So I watched like all those shows. So it was like that. It was iCarly. There was a spin-off called Sam and Cat. That one wasn't good. Victorious, Zoe 101, Summerland. They had some dope ****. Nickelodeon had some dope **** back in the day. Degrassi, obviously, you know. Ariana Grande got her start. She was in Victorious. Leon Thomas was in Victorious too. So that's why I found those two. I've known I've been fans of them for, you know, like 15 years now.
+00:17:17 Darius
+I didn't know. So there are some talented people.
+00:17:19 Jordan
+Yeah, he was a child star. Yeah.
+00:17:22 Darius
+No, I yeah, I mean, just to not leave you out there hanging, I'll give the people one. I play some pokémon.
+00:17:29 Jordan
+So appreciate it.
+00:17:33 Darius
+I'm trying to think what else. Yeah, just as far as just like things that I do that are coded juvenile would probably be playing pokémon. I mean, that's pretty bad. So yeah, that's it. I'm about to say that's like, it's so like when you play it, you can tell it's clearly designed for children because it's so easy to beat. Like it's just like The computer will throw out a fire pokémon and then you just throw out a water one and then you use a water move.
+00:18:02 Jordan
+And then it's over. Yeah. So there's no rough paper scissors. Okay.
+00:18:05 Darius
+No, it is just, it's very, you can tell it's designed for a child's brain. And like once you get into like competitive plus EV, you know, battle royales, which I don't do because I just, I'm not breeding pokémon to get extra points and all that ****. Right. But if I get super dorky, I do.
+00:18:24 Jordan
+Yeah.
+00:18:26 Darius
+So especially if I'm like remote, I'll hop on the Reddit thread. It's Brilliant Diamond Shining Pearl, so it's BDSP. And like if someone's looking for an evolved trait, I'll just help them out with that. And so like what it is, like there's some pokémon who only trade, who only evolve when you trade them. So like Kadabra evolves to Alakazam and like Graveler will evolve to Goldum, but you need to trade them to somebody and trade them back. And back when we were kids, used to have an actual trade link, a cable, we have to go to somebody's house and trade. Now it's all digital. So I'll just hop in the Reddit thread and like scroll and see if anyone's looking for a trade and be like, yeah, I got you. And just send them a link code and we'll do like. So like there's version exclusives for each, like, so there's pokémon on Brilliant Diamond that I can't get on Shining Pearl. And so like I'll be like, I'll breed you these three pokémon and then you trade me those three and then I'll go to the daycare and like breed the pokémon and send them to the internet person and then they send them back. So as Usher would say, those are my confessions. So I don't just play, I actually play. So I do. Yeah, there's like a like Saturday morning you can battle like your rival. And he gets better the more you progress. And so that's one of the first things that will Saturday morning, wake up, get situated, get breakfast and sit down and beat the rival. So nice. Can't ever say hi that pretty hanging.
+00:19:57 Jordan
+That's fair. That's lit.
+00:20:03 Darius
+Anything else for that one? I guess we never really talked about the characters. I have. As I said last week, Mike from Suits hated his guts. This one's a little controversial because people love him, but Ned Stark in Game of Thrones was not a fan.
+00:20:23 Jordan
+I hate him too. He was a horrible ******* father. He failed his children at every turn. His pride was so he was so selfish. Yes, go ahead. I didn't even cut you off.
+00:20:32 Darius
+Go ahead. No, I don't think he was a bad. I think his flaw was that he was too good. And he wanted to he wanted to live in a world, you know, he just He was a Northman and he tried to bring, he wasn't prepared for the politics of King's Landing and it ended up making his whole family worse off because of that. And so it does not sadden me when his head gets chopped off in season one, episode nine. I think it's eight. It's eight.
+00:21:01 Jordan
+So yeah, you could argue his actions bordered on suicidal, considering the world that he was living in. That's a good one. Both Moesha and her dad. They both suck. Her dad was a chauvinistic ******* and was just really mean and sexist. And then Moesha was kind of a mean girl to all her friends, especially to Kim or Countess Vaughn's character.
+00:21:30 Darius
+RIP, I think, right? She's gone.
+00:21:32 Jordan
+No, she's still here. Yeah, she's still here. That's Andel. Andel passed away.
+00:21:39 Darius
+Yeah, she's not dead. Fair enough. She's 4 foot 11 though. So that is.
+00:21:44 Jordan
+Yeah, she's just very short.
+00:21:47 Darius
+Yeah, you're right. Adele is gone. RIP Adele.
+00:21:50 Jordan
+Yeah, RIP to her. She was great.
+00:21:53 Darius
+No, I don't. As far as 90 sitcoms, season one, Uncle Phil hated him. That's right. They probably, that's probably why they rewrote the character.
+00:22:01 Jordan
+Season one Carlton too.
+00:22:03 Darius
+Season one, that whole family.
+00:22:06 Jordan
+Yeah, pretty much everyone but Will and Ashley, they sucked.
+00:22:08 Darius
+Pretty much. The Winslows was not a fan of Carl Winslow.
+00:22:16 Jordan
+Yeah.
+00:22:17 Darius
+You know, he was. He was not great. I'm trying to think. No, trying to think.
+00:22:23 Jordan
+I'd say Rachel from Friends.
+00:22:27 Darius
+That one wasn't great either. I'm trying to think. Joan from the girl from girlfriends the main lead character was not great.
+00:22:37 Jordan
+I'm trying to actually really all of them all the girlfriends were horrible people.
+00:22:41 Darius
+Well, that's probably because we're men.
+00:22:47 Jordan
+They hated each other. They were not friends.
+00:22:50 Darius
+I'm trying to think trying to think of characters who you're supposed to like. And so it's easy to just pick like Lieutenant Rawls from The Wire who was like cartoonishly evil.
+00:22:59 Jordan
+Right. Leonard could be annoying. Leonard, Leonard Hofstadter.
+00:23:05 Darius
+Oh yeah.
+00:23:06 Jordan
+He was pretty, he was pretty whiny.
+00:23:10 Darius
+I think. Who else did you have on your list?
+00:23:16 Jordan
+Oh, Monk from Monk. He was, he was kind of unlikable. I mean, he had a lot of trauma and I think I was clearly, you know, had some rain man situation going on, but he could be a lot to deal with. There's a show called Pretty Little Liars. This girl named Allison, she's like, Regina George would be like, yo, that ***** is crazy.
+00:23:39 Darius
+Okay.
+00:23:40 Jordan
+That's like, that's the best way I can describe that.
+00:23:44 Darius
+Okay.
+00:23:50 Jordan
+Protectors were supposed to like.
+00:23:52 Darius
+I'll get you one. Who was the wife and best man? Her name was Mia, right? The one who died.
+00:23:58 Jordan
+Yeah. I mean, she started that whole ****.
+00:24:01 Darius
+You know, there are better ways to get back at me and sleeping with my best man is not one of them. And not telling me, I mean, you know, not great. And I'm sure she's supposed to be likable in that movie, but I found her behavior to be a bit detestable and you can't be a bit detestable to be detestable.
+00:24:18 Jordan
+And then passing it off is like, oh, it was just a sweet, innocent moment. He took my virginity or whatever. Like, what? That was crazy. And I can't remember if she read the book too, but I feel like she probably did.
+00:24:32 Darius
+Maybe. I'm trying to think. What is a recent prominent show that we, that everyone's watched so we could just pick someone on it? I guess the problem, there's no monoculture anymore. Everyone doesn't watch the same thing.
+00:24:48 Jordan
+Yeah, there's no big shows.
+00:24:50 Darius
+It's like the laziest things.
+00:24:51 Jordan
+Too many big shows.
+00:24:52 Darius
+No, yeah, they're all, but they're all in their own like niche areas, right? You know, there's no, and like, I'm going to say Molly, and it's the least, that's the most unoriginal thing ever.
+00:25:04 Jordan
+Right, I would say everybody, most healthy people hated Molly. I.
+00:25:09 Darius
+Don't know, man. I don't really have anything else for that one, do you?
+00:25:12 Jordan
+The Tiffany 2, I wasn't offended to. from Insecure, she was awful. And the way the fact she set up Condola with Lawrence behind Ease's back, that was insane.
+00:25:22 Darius
+She just set them up. They were at the party together.
+00:25:26 Jordan
+No, remember, she introduced them before that.
+00:25:29 Darius
+So, like what?
+00:25:31 Jordan
+That's not crazy.
+00:25:32 Darius
+No. No, they were, they were broken up and they.
+00:25:37 Jordan
+I don't know, I think that's a little nuts.
+00:25:42 Darius
+I don't think so. I, people got to grow up, man.
+00:25:46 Jordan
+You think she should have at least told Isa like, hey, I'm doing this?
+00:25:49 Darius
+For what?
+00:25:51 Jordan
+I mean, they were always all in the same space. Like that, just out of respect.
+00:25:55 Darius
+These are not teenagers. These are 30 year old working professionals. Like we don't have to.
+00:26:00 Jordan
+That's fair. LA is a small town. Like that's fair. That's fair.
+00:26:03 Darius
+People got people date people break up people. Yeah, it's not easy. People got to get out of their feelings, man. I, you know, that's, you're not the main character of the universe. And her friend said he was cute or whatever. I don't know the mechanics of it. And she introduced them. And what those two grown people do is not her problem. You know, that's valid.
+00:26:29 Jordan
+And she did cheat. So it's like you did cause the breakup.
+00:26:32 Darius
+So yeah, it's just. you can't hermetically seal your exes from your entire now your inner if it been Molly or something that was dating Lawrence that's different but like your friend introduced him to her friend you just got to charge that to the gang you can't get mad about that you know that's just that's just people being people and she can't help with them two grown people gonna do.
+00:27:00 Jordan
+True and he probably would have shot a shot anyway knowing Lawrence That's fair.
+00:27:04 Darius
+He was on a tear.
+00:27:06 Jordan
+Actually, you know what? I just thought of another character from Insecure that everybody tried to act like we were supposed to like that I'd never really ****** with personally. Nathan. People are like, oh, Nathan and Easter should have been in game. She ghosted her for a month, moved to Houston, and then tried to pop back up on her birthday with some flowers.
+00:27:23 Darius
+With some cheap flowers at that.
+00:27:24 Jordan
+With cheap flowers at that. It's like. I made a comp. I made a comment about it on TikTok. I was like the same people who excuse his like bipolar disorder for him like ghosting her are the same people that say Lawrence deserve to get cheated on because he was going through depression.
+00:27:41 Darius
+That and quite a violent streak. Probably not. That's not a good sign. Men who cannot handle their temper are not. That's not a good sign.
+00:27:54 Jordan
+That is true.
+00:27:56 Darius
+And the ghosting, the cheap flowers, the popping up like nothing changed, But when it was over, he did just he did bow out gracefully. So he did.
+00:28:12 Jordan
+He did. Oh, yeah, that's true. I think that's all I got for that one. You got anything?
+00:28:17 Darius
+No, man, we can head into the next one. Just a random prompt I pulled off my list of evergreen topics. So What, phrase it two ways, what advice do you feel like you're finally old enough to understand and or what advice would you give your younger self that you are finally old enough to understand? So.
+00:28:37 Jordan
+The advice I'm finally able to understand now that I hated like when I was younger is delayed, not denied. Wanting things to happen exactly how I wanted them to happen, when I wanted them to happen. with who I wanted them to happen with and if it wasn't like on my timeline and based on what I thought I should have by then it was like I shouldn't even ******* I don't even want this anymore you know like like somebody could have liked me or I could have liked somebody they'd like me a week later I'd be like well **** this like you know **** like that also just you know not understanding the bigger picture you know when there's that phrase rejection is redirection And that's something I really have had to learn, had a hard time accepting, a lesson I had a hard time accepting. Because there was things, jobs I thought I wanted. And you look back and you're like, I probably, it's probably a good thing they didn't call me back or, you know, whatever. Or the girl I liked and it's like, you know, maybe it's a good thing that it didn't work out or that she shot me down or whatever. yeah I think that's probably one of the biggest lessons I've learned because when you can't get something that you think you're supposed to have you feel like you failed and sometimes it's not a failure it's just you know something that needs to happen so that you can get what you're actually supposed to have.
+00:30:06 Darius
+At what we need the the the what do they do in poetry the the.
+00:30:12 Jordan
+The snaps the snaps yeah.
+00:30:13 Darius
+That was pretty good that's pretty good I got over after all that I got weightlifting I was like, don't listen to your body. As I am doing a current rest week, those are important. Don't try to power through injuries. There are a few times in life where I really wish I had not tried to work through injuries. It took me a while to learn the value of preparation. Mm hmm. There's nothing I you know, I've said this before on the pod. There's nothing more overrated than winging it. It's just and you know, it's funny because I doing the pod, watching other people's content now, so much stuff that I thought was improvised, I could feel the setup. I you could just like you could just.
+00:31:03 Jordan
+Yeah.
+00:31:04 Darius
+Every podcast you that feels like they just turn on the mic and start yapping. I promise.
+00:31:09 Jordan
+No, Like that's yes. Like that's the one thing I like about like the button pod is they do like behind the scenes **** or they the **** before the show. Like they're hanging out at their studio wherever, you know, forever long before they shoot. So they've had the conversation before, they go and sit down and, you know, do the stuff.
+00:31:29 Darius
+Yeah, it's It's and it's one of those things. Once you see it, you can't unsee it. And it just right. I'll listen to like now the talented ones don't sound like they're reading from a script.
+00:31:43 Jordan
+Right.
+00:31:43 Darius
+But I would venture to guess that virtually none of the big podcasts are just totally winged. I think Joe Rogan's might be just totally winged.
+00:31:53 Jordan
+Yeah, that one for sure.
+00:31:55 Darius
+And it's like 3 hours. And I don't know how it's popular, but it is the most popular podcast on Earth. So **** it. I don't know.
+00:32:00 Jordan
+He gets good interviews. I used to I watched some of those. I've watched some of those clips before. If it's someone that I'm really a big fan of.
+00:32:06 Darius
+It's just a three hour stoner conversation. And I just can't take the meandering nature of it.
+00:32:11 Jordan
+I do wish. Yeah, I wish he'd put time stamps in those for sure.
+00:32:15 Darius
+But no, it's preparation. Pretty much anything. Almost everything I wing I ends up being worse than if I prepared for it. So just when you when I meal prep on Sunday, it makes it so I don't have to wing dinner and that helps. And, you know, just writing down my lifts and preparing for the pod and things like with work and even like even circling back to Madden, like when the off season starts, I will write down my targets. and look at the draft and which players I want and which picks I have and where I can get value here and what kind of contracts are there. I don't just I remember if I just like start a dra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Transcript
+00:00:00 Darius: 
+While we're here, when you getting on stage again?
+00:00:03 Jordan: 
+I got some bullets in the chamber. I just got to find the right time to shoot them. Metaphorically.
+00:00:08 Darius: 
+One. Out the trunk with Jordan and Darius. My name is Darius. That's D's all up in the area on all socials.
+00:00:16 Jordan: 
+And I'm Jordan. That's Jordan to be riding on all socials.
+00:00:18 Darius: 
+This podcast, two friends met in a bar, started talking and never stopped. So our segment we call What's On Our Mind, where we let you guys know what's on our mind, things we saw on the internet, pop culture, stuff like that. New different, a new different world. The Different World reboot trailer just dropped. Did you check it out?
+00:00:38 Jordan: 
+Yeah, I saw it a few hours ago when it popped up on Twitter. It looks like it's got they got a good budget. That's the first good sign.
+00:00:49 Jordan: 
+There some of the old cast is involved. That's also a good sign. Love seeing black people be employed in the entertainment industry.
+00:01:01 Darius: 
+That was a good thing.
+00:01:01 Jordan: 
+That's a third good sign. So we got three good signs in the course of a two minute, three minute trailer. It does feel again, it's just trailer, so who knows, but it does feel a bit like
+00:01:14 Jordan: 
+an old person's interpretation of what a modern HBCU is. You know what I mean? Like it just looked like the stove.
+00:01:21 Darius: 
+Yeah, it's I think it's written by Debbie Allen who wrote the original, but the original was 40 years ago. Right, Yeah. Okay, so here's my thing with these reboots. Why are they so serious? Like sitcoms are supposed to be whimsical and funny and silly and
+00:01:44 Darius: 
+They always take these like super serious tones and I don't, is that a, is there a reason for that?
+00:01:50 Jordan: 
+I watched it and that's been great. It felt heavy. Like it just felt like, it didn't feel like the fun I felt in college. You know what I'm saying? Like every day wasn't fun, of course, it was college, but you know, that just wasn't my experience. Again, it's a trailer, but you know, whatever. Yeah, I don't know. It just felt very like,
+00:02:08 Darius: 
+They did a gritty reboot of the Fresh Prince of Bel Air. So I mean, anything's possible. Yeah. You know, I just, I feel like the essence of sitcoms is that you did some serious episode, but like, I didn't get any laughs. I didn't sense any laughter in that trailer. And, you know, it's not for me. I don't, I'm not with these reboots. I think it's, I don't think it's fair to the creatives involved. Like,
+00:02:40 Darius: 
+why can't you just make something new? I don't get it.
+00:02:44 Jordan: 
+Yeah, the reboots are exhausting at this point.
+00:02:46 Darius: 
+The concept of a different world isn't really all that like unique. Just do.
+00:02:51 Jordan: 
+No.
+00:02:52 Darius: 
+And then when you brand it that way, which is probably how it got green lit, you're kind of putting them in a box and it's an uphill climb and you could have just made something else and given them an opportunity to where they can chart their own path instead of just trying to make people
+00:03:07 Darius: 
+relive something that came out 40, 40 years ago. And, I wish them the best, but I'm probably good on it.
+00:03:16 Jordan: 
+Yeah, same. It almost gave me shades of that. Have you seen that show, Dear White People?
+00:03:22 Darius: 
+I have not. No, I did. The title alone was a non-starter for me.
+00:03:26 Jordan: 
+Right. Yeah, it gave me a little bit of shades of that. Like, Grown-ish was a sitcom.
+00:03:34 Jordan: 
+you know, in the spinoff of Blackish obviously, but like, it felt like still like fun college kids, you know, there was still like a lightness to it, even though it was a bit melodramatic, you know, I don't know. It felt, yeah, it felt almost like a, like remember like the, the last like hour of like you got served before everybody like came back together again. Like that's kind of what it felt. Remember the sequence where like,
+00:03:59 Jordan: 
+Marcus Houston gets robbed and like they play the Hamilton song and like Omar Young's dancing in the rain and like, we're just like, stop being fun for like 15 minutes. Like, that's kind of what the vibe I got.
+00:04:11 Darius: 
+Are you going to watch it?
+00:04:14 Jordan: 
+Probably not. Actually, funny story. So I was, I was in Charlotte this weekend. I was hanging out at a friend's crib and we were watching, we're like hungover, just like looking for something to watch on TV and on Netflix.
+00:04:27 Jordan: 
+And we've talked about streaming content and how it's tailored to people not watching and stuff like that. And it's just, everything's over explained or whatever, how just the quality is so bad. When you're leaving from the watch and you just scribe, swipe through all the trailers in a 5 minute period, you're like, holy **** it's all true. Like sometimes you're like, oh, they dramatize it. Like every streamer shows can't have bad content, which they don't. But Netflix is really like the bottom shelf.
+00:04:48 Darius: 
+No, I mean, it's just all swap. Like if you scroll through and sometimes I'll read a
+00:04:55 Darius: 
+a description. I'm like, that sounds like a decent movie. And I look and it's like 8 episodes. I'm like, what? It'll be like the description will be like, you know, mom comes home because her dad died and she meets her like high school love. And it'll be like 8 episodes. Like how the **** you get 8 hours out of that? There's no way.
+00:05:15 Jordan: 
+Right.
+00:05:16 Darius: 
+That's a that's a stretch to get a movie out of you.
+00:05:20 Jordan: 
+No, yeah, for real. It's a homework movie.
+00:05:22 Darius: 
+You just like there's this the diplomat
+00:05:25 Darius: 
+And that was like the third episode. And I was like, I don't have the nothing is going. This is a show about gibberish. It is just, it's all bad. Like none of it's any good. All the documentaries are slop. If it's not a movie that was made somewhere else and licensed to Netflix, it's going to be bad.
+00:05:44 Jordan: 
+Right.
+00:05:44 Darius: 
+I think if it's made by Netflix for Netflix, it's terrible. All of it's really bad.
+00:05:51 Darius: 
+Only reason I have Netflix, I get it for free with my cell phone now. Otherwise, I didn't have it for a year because it was it's junk.
+00:05:58 Jordan: 
+Yeah, they I mean, I go there because they have some of the good movies that keep getting taken off every streaming service because it's a constant shell game. Yeah, other than that, I don't know. I forget I have it most of the time. I'm usually watching Amazon or Disney Plus.
+00:06:11 Darius: 
+I hear you, man. You want to head into our first topic?
+00:06:14 Jordan: 
+Yeah, what we got?
+00:06:17 Darius: 
+Everyday tasks.
+00:06:19 Jordan: 
+Oh, yeah. So
+00:06:21 Jordan: 
+I've just been like thinking about like, you've had those periods where you're like, you know what? I'm just not doing that. It feels performative and a waste of time. And it feels like that's like where I'm at, which is like a lot of adult, quote unquote adult or like homemaking tasks. One of them being ironing. I just throw my clothes right in the dryer and I know it takes longer, but whatever.
+00:06:45 Darius: 
+You better just wear them wrinkled. I don't care.
+00:06:51 Jordan: 
+The rumors I'd be late sometimes, like what I usually do is like before I get in the shower, I'll take the clothes, put them in the water a little bit so they're like damp and then throw them in the dryer to get the wrinkles out on a high speed. And then I'll just shower and game until my clothes are ready.
+00:07:05 Darius: 
+I've been in my current place three years next month. I don't think I plugged my iron in one time.
+00:07:12 Darius: 
+I'm not ************. I believe that. In fact, I believe you zero times. In the last unit, maybe, because I've stayed there 10 years, but in this one, it'll be three years in September. I have not, I could have left my iron in the old spot and I would have never noticed. Like I just, you know, that one's out. That was the one I had, because I didn't really know where you were going with it.
+00:07:37 Darius: 
+I'm glad you didn't say like bathing, but.
+00:07:39 Jordan: 
+Oh, yeah. No, I do that every day.
+00:07:43 Darius: 
+But now I am. I do not iron. I can't. I can't do it.
+00:07:48 Jordan: 
+Yeah. I feel you. Yeah. There's some dryers now that have a D wrinkle setting, like basically just completely replacing the iron, which does
+00:07:56 Darius: 
+anyone under the age of 50 still iron? Do you know anybody, any of your peers, friends? Anybody?
+00:08:02 Jordan: 
+I know a lot of people who don't iron. I talk about this with other people and they say the same thing. I mean, I think like I iron dress clothes because you can't get out of not doing that. Other than that, I pretty much don't do it. Yeah, so that's one for sure. Another one, I've always felt this way since I was a kid. Making the bed just feel so performative. It's like I sleep in it. People know I sleep in it. Why don't people like I don't sleep in it? Who are we putting this show on for? This is not a movie.
+00:08:32 Jordan: 
+As long as your sheets are clean, I don't see the problem.
+00:08:37 Darius: 
+Well, so I have been called out. Like I posted a selfie with a wrinkle bed and this woman I had a crush on called me out for it. And so I've been, I'm a bit cognizant of that, but just like on the day to day, I might take one selfie a week. So it's not even really like, I'm just not a picture person. So on a day to day,
+00:08:58 Darius: 
+That bed is going to look like it did at 10 A.m. at 10 P.m. at dawn.
+00:09:05 Jordan: 
+Yeah.
+00:09:06 Darius: 
+I only vacuum once a week now. I feel like vacuuming every day is performative as hell.
+00:09:09 Jordan: 
+Yeah, every day is nice. I'm sorry. Unless you have like a husky. I don't get the point.
+00:09:14 Darius: 
+I do have a cat, but so they should. I vacuum once a week the whole place.
+00:09:21 Darius: 
+And then another time a week, when I get ready to fold my clothes, I don't use like a folding board. I just literally, in my spare bedroom, dump all the clothes on the floor, fold them all, put them in a basket, put them up. And so I iron that, I vacuum that room out first so I don't pour my clothes all over cat hair. Dirty. So that would be stupid. So that's, so that room gets vacuumed twice a week, the rest of this place once a week. So Gotcha. Anything else?
+00:09:50 Jordan: 
+It's funny, he brought up another one I was going to say, folding clothes. That's like really a problem for me. It's a sign of like,
+00:09:57 Darius: 
+it's probably leading to the wrinkles. We're establishing a chain of chain connection here.
+00:10:06 Jordan: 
+You know in therapy to say it all connects.
+00:10:08 Darius: 
+Yeah, I guess so.
+00:10:09 Jordan: 
+I literally, I literally, like I take my clothes and I ball them up and I put them in the drawers.
+00:10:15 Darius: 
+Oh no, hell no.
+00:10:20 Darius: 
+I don't not right away because like Sunday is the big laundry day because that's like the meal prep day prepare for the week. So I wash my bed sheets and swap those out on Sunday. And I do a big load of clothes like my hamper, which is just kind of like everything I wore through the week, you just throw in a hamper. And I fold that stuff Monday. And then so it sits for a day. I don't fold it right out the box.
+00:10:49 Darius: 
+And then I wash, I work out all week and then I do a cycle of gym clothes on Friday because that's too sweaty and nasty to sit for a whole week. And so I fold those up right away because I need to wear them and go back to the gym because I only have four sets of gym shorts. And, so, but I'm with you. They sit for about 24 hours. And I can't do. Do you still separate the darks and the whites?
+00:11:17 Darius: 
+Not gonna be able to do it.
+00:11:19 Jordan: 
+No, I didn't go sit up here and perform for y'all. No, I do not.
+00:11:23 Darius: 
+No, I mean, they're mad.
+00:11:24 Jordan: 
+I won't watch like a red shirt with a white dress shirt or something like that, obviously. But other than that, no, I don't do that.
+00:11:31 Darius: 
+Listen, man, I shop at Amazon and Old Navy. So if this shirt that costs $20 gets ruined in the dryer, we'll just get another one. I'm not. I'm not going to be.
+00:11:43 Darius: 
+Right, yeah. **** that. All that shit's going in there. And you know, I'm not separating. The hamper goes in with four Tide Pods, not even Tide Pods, generic Amazon pods.
+00:12:02 Darius: 
+Yeah. And, whatever comes out, comes out. And it's cool with that. And like, I'm pretty strict on like, once a clothes, once clothes look like worn, they're out there, they become gym shirts or pod shirts or whatever. I won't wear them out, But I'm not big on the maintenance part, man. Cause like, I hear you. What's the point of being delicate about a shirt that costs 30 bucks, 20 bucks? You know, like what?
+00:12:27 Darius: 
+I'm not the designer, so it don't matter.
+00:12:30 Jordan: 
+Yeah, same here. Like I work remote, so I'm not really going anywhere pretty much during the week for the most part. Like I go to the gym and I go out on weekends and that's for new ****. So like I don't need like my fresh **** until the weekend. So I don't really worry about that until the weekend. During the week I'm washing gym clothes. And sometimes if I don't feel like doing laundry, I'll just buy more gym clothes. I'm gonna go out of you. So I'll be like, I can just wait a day on Amazon to get me some new shorts and I'll go tomorrow.
+00:12:54 Darius: 
+That's a flex man. We're gonna brush your shoulders off.
+00:12:58 Darius: 
+Somebody's got money out here. No, I do not. I have four. Well, so I wear tank tops or like plain white t-shirts at the gym. But I mean, I have a stack of those because they're basically shirts that I used to wear out that just became gym shirts. But the shorts, 4 pairs, black, black, blue, gray in a four short rotation. We watch them on Friday.
+00:13:22 Darius: 
+to get me for the next days. And, you know, and once one gets a pair, a hole in it, that's when we replace it.
+00:13:28 Jordan: 
+So yeah, I ripped my shorts when I was out one night downtown. I still don't know how that happened. And I was like, you're like one of my favorite shorts. And they're like broken in perfectly where they didn't look dingy and they were perfectly comfortable. You know, I was pretty sad about that. So I had to buy some new shorts, getting used to them. It's an adjustment.
+00:13:48 Darius: 
+I did get some less of the feedback from our episode. We talked about the dress code at Tuskegee.
+00:13:54 Jordan: 
+Oh yeah.
+00:13:55 Darius: 
+And I was like, you know, it's like totally like, why are your jeans uncomfortable? Maybe they don't fit. And I did get a text and the person was like,
+00:14:06 Darius: 
+I had to cut off the podcast at that moment because I'm currently wearing jeans that are uncomfortable. You personalize that, not me. But no, like if you find yourself doing Olympic stretches to get into your jeans, might be time to reevaluate.
+00:14:24 Jordan: 
+Yeah.
+00:14:25 Darius: 
+Just your clothes shouldn't make you uncomfortable. Obviously some clothes are more comfortable than others. But like, I don't know the jeans I wear are not like burdensome.
+00:14:36 Darius: 
+I think they're fine. I don't know.
+00:14:39 Jordan: 
+I feel like that Beyonce line cut a lot, give a lot of people reason to cut themselves some slack with the whole like, you got to jump to put your pants on thing, you know. But shout out to the ladies who do have to jump to put their pants on, you know, I appreciate and respect y'all tremendously in all facets of life. What else was I about to say? Oh, you know what? It's funny. I was talking to some friends this weekend about, and I was like talking about my, I remembered a conversation I had with the Uber driver like a month or two ago.
+00:15:04 Jordan: 
+We're talking about working out in the gym and fitness and stuff, whatever. And I was like, the crazy part is like, how long it takes you to realize it's you that's getting bigger. Cause like for me, it was like, first I was like, oh man, like my shirt shrunk. Like damn, I love the shirt. Then it was like, but it slowly evolved. Then it was like,
+00:15:24 Jordan: 
+more than one of my shirts shrunk. And I'm like, that's weird. Maybe I'm using like too much heat in the dryer. And then I was like, not my pants too. And then I realized it was me. I'm the problem.
+00:15:38 Darius: 
+Yeah, it is true. It is true. It's hard to buy bigger clothes because it feels a little like accepting.
+00:15:48 Jordan: 
+Yeah, it feels like giving up.
+00:15:49 Darius: 
+It really does. But no, man, if you find
+00:15:54 Darius: 
+all the listeners out there, if you find a large portion of your clothes are not comfortable, there's a purchasing issue. Like, you shouldn't, it's fine. Like sweatpants are fine, but they're gym clothes and house clothes. They are not outside clothes.
+00:16:09 Jordan: 
+At work, we call that user error.
+00:16:11 Darius: 
+Yeah, you know, and prioritizing comfort at all times is what for children. Like children wear comfortable like Velcro shoes because they can't be uncomfortable for more than 5 seconds, but you're an adult.
+00:16:22 Darius: 
+And you can go. You don't need to wear Velcro shoes and comfy pants everywhere.
+00:16:30 Jordan: 
+Yeah, no, the seven part is real because I've talked to people like, you know, when you kind of realize when you when it, you know, when it hits for you and they'll be like, you know, it's usually the jeans that's to give away. They're like, Oh, my jeans don't fit anymore, you know, whatever. And then you got to buy new clothes. And and that does feel that does hurt for sure because you're like, ****. But eventually those clothes, they'll fit and you get used to them.
+00:16:52 Jordan: 
+And then you work, work hard and then there they'll be too big for you, which is nice. It's a good reward.
+00:16:59 Darius: 
+And it feels a lot better when you have when you get to throw away the big clothes. And so yeah, like it's just it's a feeling you hesitate at first because you don't want to have to go back and buy them again. But there comes a point where it's like two sizes down, you throw away the two sizes up.
+00:17:20 Darius: 
+And it feels great, And so, it's like the whole fall down the mountain, getting up thing. So there you have it. Any other tasks?
+00:17:31 Jordan: 
+I think I've decided to stop. I think I've decided to retire. So I will be no, I'm just kidding.
+00:17:40 Darius: 
+Retire what?
+00:17:43 Jordan: 
+Oh, yeah, you, yeah. No, I love what I do.
+00:17:52 Jordan: 
+No, just, I mean, I feel like being responsible is annoying, but it does have benefits. So just getting used to the benefits of the annoying responsibilities we have.
+00:18:05 Darius: 
+I don't find, I find irresponsible cool, man. Today I reorganized all of my photos for like 10 years. It felt good when it was done. It was a good time. So I had a cross.
+00:18:19 Darius: 
+my cell phone, all my old phone backups, my Google photos, my OneDrive photos. And I wrote a Python script to scrub all of those, move them into one master folder and sort them by year and then within the year by month. And then I was able to delete all that junk.
+00:18:42 Darius: 
+and keep it in one folder and I was able to back it up and it was good.
+00:18:45 Jordan: 
+Nice.
+00:18:46 Darius: 
+Organizing things and it's, I don't know, like you grow to appreciate it and when it's done and you build the infrastructure out and every day you build on that infrastructure and it makes, it's easier to accomplish tasks when you have the infrastructure there and you can build on it.
+00:19:03 Jordan: 
+Yeah, that's very true.
+00:19:05 Darius: 
+You want to head, or I guess this next one is mine. Just a general prompt, take it wherever you want to take it. Have we made success to public?
+00:19:16 Jordan: 
+Okay. It's tricky because it's really a double-edged sword because I, in general, yes, because of the culture of comparison, we're living now with social media. Like when you're not in a good place or if you feel like you're not where you're supposed to be in life,
+00:19:32 Jordan: 
+And all you see is everyone's wins and everybody's highlights. You know, it just it does make you feel worse about yourself. So in that standpoint, yes. But I also think people need to see people win to know that it's possible to get a win. You know what I mean? So from that standpoint, it's it's it's it has its advantages as well. I guess it depends on the way the win is.
+00:19:57 Jordan: 
+the success is being presented. If it's like a money spread, maybe not. You can keep that for the close friends. But if it's you getting a new job or something like that, then you should share that with people or can share that with people.
+00:20:13 Darius: 
+Anytime I see someone with like a large wad of cash, I'm like,
+00:20:20 Darius: 
+Why?
+00:20:23 Darius: 
+I cannot remember the last time I had over, I don't know, $100 in my wallet just because what's the new, like it's beyond, it's just, it's at this point with the way the world works, having a bunch of cash is inconvenient.
+00:20:40 Jordan: 
+You're actually losing money, Lucky.
+00:20:41 Jordan: 
+Yeah.
+00:20:41 Darius: 
+Well, not even that, it's like,
+00:20:44 Darius: 
+You have to keep it on you somewhere.
+00:20:45 Darius: 
+Like you have to put it in your pocket.
+00:20:47 Darius: 
+Your pockets are big.
+00:20:48 Darius: 
+And if you lose it, it's just gone forever.
+00:20:49 Darius: 
+It's something it's it makes you a target.
+00:20:51 Darius: 
+It's just high stress.
+00:20:53 Darius: 
+Whereas you could just like there's you could put it on a card and or on your Apple Wallet or Apple, whatever, Apple Pay.
+00:21:00 Jordan: 
+Google Wallet, whatever your phone.
+00:21:02 Darius: 
+Yeah, everyone takes it.
+00:21:03 Darius: 
+There's no it's
+00:21:05 Darius: 
+Cash used to be the most convenient way to pay for things, but now it's fine.
+00:21:09 Darius: 
+And anytime I see someone with a bunch of cash, I'm not going to lie, my spider sets start tingling.
+00:21:14 Darius: 
+Like, we're just...
+00:21:21 Darius: 
+There aren't a lot of...
+00:21:26 Darius: 
+There aren't a lot of legitimate means for which someone would just have $10,000 in cash in their pocket.
+00:21:30 Darius: 
+Right.
+00:21:31 Darius: 
+Yeah, It's.
+00:21:34 Darius: 
+That's not from a paycheck.
+00:21:35 Darius: 
+You know, that's not.
+00:21:36 Jordan: 
+No, right.
+00:21:37 Jordan: 
+Because if it was, you'd keep it in your bank.
+00:21:40 Darius: 
+If you ran a business, you wouldn't just accept someone's duffel bag money.
+00:21:43 Jordan: 
+You would just have.
+00:21:44 Darius: 
+Well, depending on the business.
+00:21:45 Darius: 
+If you ran a business with which you pay taxes, it's just like, how does one come about a large sum of cash in 2026 that is not shady?
+00:21:54 Jordan: 
+Yeah, unless you're like a bartender.
+00:21:56 Jordan: 
+I got work concessions after college, after graduation for a few months.
+00:22:03 Jordan: 
+And so I just like always had a **** ton of cash.
+00:22:06 Jordan: 
+And I had a legitimate job in the house.
+00:22:08 Jordan: 
+I had graduation money.
+00:22:08 Jordan: 
+So that was like a lot of cash.
+00:22:10 Jordan: 
+And I remember I took it to the bank and I felt like they probably thought I had like been selling drugs like that.
+00:22:15 Jordan: 
+You know what I mean?
+00:22:17 Jordan: 
+But it makes me think of that viral.
+00:22:18 Jordan: 
+You do realize that was 10 years ago, right?
+00:22:21 Darius: 
+Oh yeah, for sure.
+00:22:21 Jordan: 
+For sure.
+00:22:22 Jordan: 
+Yeah.
+00:22:24 Jordan: 
+Unfortunately, yes.
+00:22:28 Darius: 
+That was before Google, Google Wallet and Apple Pay.
+00:22:31 Jordan: 
+True, yeah, that's true.
+00:22:32 Jordan: 
+I had a bunch of has in college in 1970.
+00:22:34 Jordan: 
+I just had to.
+00:22:34 Jordan: 
+I just had it.
+00:22:35 Jordan: 
+It's back when we came back from the war.
+00:22:41 Jordan: 
+No, it makes me think of that.
+00:22:42 Jordan: 
+You ever saw that viral clip of Jim Jones?
+00:22:44 Jordan: 
+He was like doing it, recording a live podcast episode.
+00:22:47 Darius: 
+Yeah.
+00:22:47 Jordan: 
+And he like was trying to like make cash slip out of his pocket on accident.
+00:22:52 Jordan: 
+And so he's like slumping in his chair and he's like moving his hand in his pocket to get it to spread out.
+00:22:57 Jordan: 
+And they're like, oh, you dropping bread.
+00:23:00 Jordan: 
+He's like, oh my God, it's so embarrassing.
+00:23:02 Darius: 
+Like, you know, I just don't.
+00:23:06 Darius: 
+It's like the word, like cash is legit beyond just inconvenient.
+00:23:09 Darius: 
+It's like, especially for those dudes who have large lump sums of money.
+00:23:12 Darius: 
+It's just, it's like the worst place that you could just put it in a bank account.
+00:23:18 Darius: 
+And that like, if you lose a credit card, you call, they cancel it.
+00:23:21 Darius: 
+They send you another one.
+00:23:23 Darius: 
+You lose a lot of cash.
+00:23:25 Darius: 
+Ain't even no point in calling.
+00:23:27 Darius: 
+Like it's over.
+00:23:27 Darius: 
+Like it's gone.
+00:23:28 Jordan: 
+Right.
+00:23:28 Jordan: 
+What are you going to do?
+00:23:29 Darius: 
+There's nothing for you to do.
+00:23:30 Darius: 
+It's just chalk it up.
+00:23:32 Darius: 
+It's over.
+00:23:33 Jordan: 
+Yeah, you're done.
+00:23:34 Darius: 
+But to get back to the topic, I think I'm with you.
+00:23:40 Darius: 
+It's important to share wins, but I do think people overshare.
+00:23:44 Jordan: 
+Yeah.
+00:23:45 Darius: 
+Like I maintain that a big reason why a lot of companies had RTO.
+00:23:50 Darius: 
+Initiatives is because of those day in the life videos where people weren't doing any damn work.
+00:23:55 Darius: 
+It's like, yes, I'm not knocking what you do, but why are you making the block so hot?
+00:24:00 Darius: 
+Like you really should.
+00:24:00 Jordan: 
+No, seriously, seriously.
+00:24:02 Jordan: 
+Like, y'all are the reason we have to drive once a month or twice a month or whatever your remote or hybrid schedule is just to perform for what?
+00:24:12 Darius: 
+It's like, you never want to call attention to how little work you're doing.
+00:24:17 Jordan: 
+No, you do not.
+00:24:19 Darius: 
+Never a good idea.
+00:24:20 Jordan: 
+You want to look like you're on the verge of death while you're at work.
+00:24:23 Darius: 
+Yeah, because somebody's going to ask, well, why are they even here in the 1st place?
+00:24:26 Darius: 
+I'm not doing anything.
+00:24:28 Jordan: 
+Yeah.
+00:24:30 Jordan: 
+I saw this tweet a couple days ago and someone was like, the best part about working from home is you can just say you have internet issues and go to the gym.
+00:24:37 Jordan: 
+And someone was like, y'all still haven't learned to shut the **** **.
+00:24:42 Jordan: 
+Also, what job are you working where you can just disappear for an hour and a half?
+00:24:45 Jordan: 
+Dude.
+00:24:47 Darius: 
+Yeah, I think it's like, I can't say that, but yeah, you really shouldn't be like, I do think it's like a bit of a misnomer because even in the office, no one is grinding out eight straight hours.
+00:25:02 Darius: 
+Like that's not how it works.
+00:25:04 Darius: 
+You know, I've been in an office, I've been remote.
+00:25:08 Darius: 
+There's a lot of BSing in both ways, but yeah.
+00:25:12 Darius: 
+You just, it's like, it's, that don't rub the company's face in it.
+00:25:18 Darius: 
+Just keep it low, keep it cool.
+00:25:20 Darius: 
+Like, you know, act like you've been there.
+00:25:22 Darius: 
+You know, there's also there's a difference in how you do it.
+00:25:25 Darius: 
+It's one thing to, on a slow day, watch a movie while you're still green and available if something comes up.
+00:25:33 Darius: 
+And it's another thing to just be outrunning errands.
+00:25:34 Darius: 
+Like that's.
+00:25:36 Darius: 
+Right, Like be home.
+00:25:38 Darius: 
+Yeah, there's a way you, like, there's a way you could even slack off with strategic, like you'd still need to be available, but like, if someone calls you or asks you to hop on a call and you know, you're at Starbucks, that's gonna look a lot worse.
+00:25:54 Darius: 
+But if you were at the crib watching Game of Thrones and you just, okay, cool, hopped on.
+00:25:59 Jordan: 
+Yeah.
+00:25:59 Darius: 
+That's how you, like there's a way to use.
+00:26:02 Jordan: 
+Grab your headset or whatever you got to do.
+00:26:05 Darius: 
+No one's saying you got to just grind out eight hours because you're working remote, but there's a way you do everything, you know, like, don't be outrunning errands and **** in the middle of it.
+00:26:14 Darius: 
+I mean, you got to run a package.
+00:26:16 Darius: 
+Okay.
+00:26:17 Darius: 
+That's one thing if you got, you know, whatever, but you know, be strategic about it.
+00:26:20 Jordan: 
+So yeah, I agree.
+00:26:22 Jordan: 
+Yeah.
+00:26:24 Jordan: 
+Yeah.
+00:26:25 Jordan: 
+And it's like, have you ever been in like any work meetings where someone's like, obviously driving?
+00:26:31 Darius: 
+Or you see the teams and it's a cell phone and it's like, yeah.
+00:26:36 Darius: 
+Yeah.
+00:26:36 Darius: 
+Okay.
+00:26:36 Darius: 
+Your teams doesn't work.
+00:26:37 Darius: 
+Okay.
+00:26:38 Jordan: 
+Okay, bro.
+00:26:40 Jordan: 
+I'm glad you had fun at the mall.
+00:26:42 Darius: 
+Yeah.
+00:26:43 Darius: 
+You make it the black hot.
+00:26:45 Jordan: 
+Yeah.
+00:26:47 Darius: 
+But no, I think as someone who's pretty private, I get I
+00:26:54 Darius: 
+I get both sides of it, but I do think oversharing is a bad.
+00:27:01 Darius: 
+Also, people overshare too much negatives about their lives.
+00:27:03 Darius: 
+Like we really don't need to.
+00:27:06 Jordan: 
+There are some people and I'm like, have you ever had a good day?
+00:27:08 Darius: 
+Or just like, why are you?
+00:27:10 Darius: 
+posting your emergency room visit.
+00:27:13 Darius: 
+We really don't need to see like your head busted open getting stitches.
+00:27:17 Darius: 
+Like that **** that's like, that sounds like a family personal type.
+00:27:22 Darius: 
+Like why all 400 of your followers need to see you like your gushing blood wound from whatever, you know.
+00:27:28 Jordan: 
+Yeah, that's a good one.
+00:27:30 Jordan: 
+Yeah, that's a good one.
+00:27:31 Jordan: 
+I think people underuse close friends.
+00:27:35 Jordan: 
+You know, some **** you just keep for your inner circle.
+00:27:40 Jordan: 
+And then also I think there's a fine line between like sharing your loss because I do think you should share some of your losses because like this is real life, But where it gets to the point where it's like, okay, like, dude, this like every day is something with you.
+00:27:55 Jordan: 
+Every day it's a paragraph post.
+00:27:57 Jordan: 
+Why?
+00:27:59 Darius: 
+My favorite is like the just text that person post where the like,
+00:28:05 Darius: 
+now I'm the evil person because I decided to call you out.
+00:28:08 Darius: 
+Just please take us out the group chat.
+00:28:10 Darius: 
+Like this is for an audience of 1.
+00:28:13 Darius: 
+Just that person.
+00:28:15 Darius: 
+Like I don't, why do I have to be a party to this?
+00:28:19 Jordan: 
+Or it'd be the people who like, who are always like posting like emo **** and it's like very clearly performative where it's like, no one has one back but me, I'm alone in this world.
+00:28:28 Jordan: 
+And it's like, you have a loving family and a full social circle.
+00:28:30 Jordan: 
+What the hell are you talking about?
+00:28:33 Darius: 
+That is the absolute worst, man.
+00:28:34 Darius: 
+It's just, you know what I actually hate?
+00:28:40 Jordan: 
+Yeah.
+00:28:42 Darius: 
+The pedicure posts where they take a picture of someone like rubbing their feet and it's like, they're paying for a service.
+00:28:51 Darius: 
+That's fine.
+00:28:52 Darius: 
+I get it.
+00:28:53 Darius: 
+But like, do they consent to this photo of being like, look at this slave I hired.
+00:28:58 Darius: 
+They're rubbing my feet.
+00:29:02 Jordan: 
+Look at these peasants.
+00:29:05 Darius: 
+I just threw her some crumbs and she was like, some breadcrumbs and she jumped.
+00:29:08 Darius: 
+It's like, okay, I get that.
+00:29:10 Jordan: 
+Yeah.
+00:29:10 Darius: 
+She's probably well compensated to be honest with you.
+00:29:13 Darius: 
+And you're going to tell me, that's fine?
+00:29:14 Jordan: 
+And you're probably overpaying, to be honest.
+00:29:17 Darius: 
+The imagery is really bad.
+00:29:19 Jordan: 
+It does.
+00:29:19 Jordan: 
+It does look very ill.
+00:29:20 Darius: 
+Scrubbing your feet.
+00:29:22 Darius: 
+They're wearing a mask.
+00:29:23 Darius: 
+They're not asking for this photo.
+00:29:24 Darius: 
+They've been at work all day and it's like.
+00:29:26 Jordan: 
+Right.
+00:29:26 Jordan: 
+They hate your guts.
+00:29:28 </t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:00 Darius
+The more stuff I read on it, the more I could, the more time passes, the more I'm convinced that smartphones are cigarettes. And in 100 years, they're going to, people are going to look back on us with our phones and our hands. Like we look back on those pictures of people smoking in restaurants. Like I cannot believe that's how people lived. Like they really like sat there.
+00:00:19 Jordan
+Oh my God, they had smoke in here.
+00:00:21 Darius
+Yeah, like they just smoked on an airplane and you know how we look at that. Like that's just insanity. Like they didn't know that they were killing themselves. That's how people will look at us, staring at our phones all day. Welcome to Al the Trump with Jordan and Darius, the podcast where two people started talking at a bar and never stopped. I'm Darius. That's these all up in the area on all socials. And I'm Jordan.
+00:00:41 Jordan
+That's Jordan to be writing on all socials.
+00:00:43 Darius
+It's our segment we've titled What's on Our Mind. That title is permanent now. So we are not changing it. It's already branded. So appreciate all of the suggestions of which there were zero, but we're not. But thank you anyway. The segment where we let you guys know what's on our mind, what we saw on the internet, things that we wanted to talk about. We always like to start, well we, not always, but sometimes we start with an opening salvo where we kind of, just find something under there we can talk about and let you guys know who we are. So sent you the graphic, we're going to put it on the screen there. You got six houses to choose from. Which one you picking?
+00:01:21 Jordan
+Yeah, I'm going to go with house number six. It's got the house tub, wow, house tub, hot tub, mountain view, movie projector, wine cellar, hopefully house tubs also. Yeah, I love nature, just sitting outside, being outdoors. So anything that allows me to kind of do that is nice. I'm assuming it's got a lot of windows, which gives her natural light, hopefully an open floor plan. That's a little bit of architecture preference for you guys. Know a little bit more about me. Love a hot tub. Big movie guy, so movie projector is kind of a must. And then a wine cellar. I'm not a big wine guy, but if I have a dream home, so to speak, then I'll be hosting A lot. So I would need wine to host.
+00:02:02 Darius
+I would say number six was my second choice. But honestly, it's. Well, I'll just say my first choice right now is my first choice is number four. Yeah. I will admit I will concede off the top that the big dog is kind of a net negative it takes away. But the other three are so positive that they kind of override the fact that, you know, big dog, I'm sure they're great and But that's a lot of work. And when you're building your dream home, you're thinking about leisure, not work. So start at the top with a swimming pool. Women love swimming pools. I could take them or leave them, but that's a nice little amenity to have at the crib, especially when you like to host and different things like that. People like to get in the pool and I like to be a good host. And so margaritas like to have margarita in the pool, nice little summer day. Good times, good vibes. I'm A tequila man myself. So nothing wrong with a little tequila and Kool-Aid, which is basically a margaritas are. Master grill. 90% of the reason I want to buy a home is because I miss grilling A lot. I'm a pretty good griller. I don't know if griller is a word, but I'm pretty good on the grill. And you know, it's when you live in an apartment, grilling has to be like an event. You have to It's much more of a logistical challenge than if you just have a house and you could just throw some burgers on. And so I would love to have that option. Big dog, I've already admitted is just, I can't really, I don't really care for that. So that would be my choice. My #2 choice would be the hot tub. Did you have a #2 choice?
+00:03:47 Jordan
+Yeah, #2 for me would be. I go house 5. I like the idea of having different random things in one home, to kind of make it unique. So I feel like nothing's more unique than a garden, a library, and a coffee bar all in one place. I'm more of a dog guy than a cat guy, so I just have to deal with that. But I'd let them climb around the library. I'm assuming it's very spacious. You know, that's like climbing things is fine. Did do some gardening stuff growing up with my dad and my siblings. We grew like fruits and vegetables in our yard for a little bit. So that was fun. And then a coffee bar, great for tea, warm beverages in the wintertime, cocoa and all that kind of stuff. So you can't go wrong with that. And also who doesn't love the vibe of a coffee shop?
+00:04:41 Darius
+I do love a coffee shop and I do love a fancy coffee. It's like I have a latte machine and I really only use it on Sundays because it's a bit it's labor intensive and it's the amount of caffeine I drink. I can't I can't make three or four lattes. It's just too much work, but it is dope to have. So just real quick, if you could pick one item from each row to build your perfect for for for collection of four items, which quartet. Yeah, that's the word we're looking for.
+00:05:13 Jordan
+Yeah, I'll go. Top row, I'm going swimming pool. I love swimming. I love the water, lakes, oceans, any body of water I love swimming in. Number 2, I'm going, I go, I'm gonna stick with the mountain view. It's the most unique of those choices. Number 3, I'm gonna go with the fire pit. Be great for summertime, making s'mores, roast the marshmallows. You know, playing some music, smoking cigars out there with the squad or whatever, with, some friends and stuff. And then #4, I'm going, yeah, I don't have the patience for a dog like full time. So I'm going to go with a wine cellar. And I don't know what I do with a fishing pond. So yeah, I'm going to go with a wine cellar.
+00:06:08 Darius
+For me, number one is swimming pool. I think that's of all of these, all 4, 8, 12, 16, all 24 amenities, the swimming pool is number one on the list. Number 2, I'm going with whiskey. I'm usually a tequila man, but I just feel like whiskey is a booze more befitting of, you know, my fancy home, you know, my warm and fancy home. Number three, we're going to keep the grill. Yep. Just feel like that's one of the biggest benefits of owning a home is that you get a giant, you can have a grill and a smoker and you can just, you know, it adds so much more to your cooking options and you know, we love options. And #4, it's between wine cellar and endless snacks. So I'm going to go with wine cellar just because I like wine. I don't drink it very often. just because I don't really keep it at the house and I don't really order wine when I go out because most bars have terrible wines. And so a little wine to let the crib, some fancy stuff with a steak from the grill. Who can argue with that? So I want to head into our first topic. Believe it's yours.
+00:07:23 Jordan
+Yes. Okay. So what makes a good protagonist? I was actually talking about this with a friend at a party this weekend. I was venting about the show House of Dragons and why the season been a flop. One, because nothing really happens in the show. And 2, because the main character is profoundly unskilled and uninteresting. She doesn't make any real choices or decisions. She waffles over everything so she doesn't actually do anything. She has dragons, she doesn't really use them for the most part, or doesn't use them what they're for, you know. Not a skilled fighter, so it's just like, what are you, she's kind of the anti-Cerci's low key. So you got me to think about what makes a good protagonist in order to drive a good story. So I wanted to ask you about what are some of your favorite protagonists and what traits do you value the most in a protagonist in a story?
+00:08:14 Darius
+Value the most, I would say, if I could put it in one word, it's competency. It doesn't I don't have to like you or dislike you, but I can't think you're stupid by and large. Some shows I can and it's fine. But I can't feel like the writers are keeping you alive. I have to feel like you are keeping yourself alive or I mean, some shows the stakes aren't that high, but you know what I mean. Like you're not succeeding because you were written to succeed. You're succeeding because the character as written would have made these moves and is smart and doing the right thing. And so, yeah, that's prior that's probably one of my, that's my most affirmative thing that I need. And the thing that I can't have is I just can't have an overly emotional crying protagonist. Like is a lead, is a lead man and you got like 2 cries before I'm out. Like I can't, I, you know, I don't really do too much crying as grown men. So what about you, man?
+00:09:12 Jordan
+So I'll pick up about that, but I'll just go macro. I hate a weak protagonist, period. A protagonist that just is not willing to do what's necessary. I just have really no patience for them, to be honest. They really bug me. A protagonist who I need a protagonist who is interesting, who's willing to make a choice whether it goes well or not. You can always amend, not always amend it, but that's what, you know, life and story is, you know, I need them to be principled in whatever, not everything they do, but just have some sort of principle and some sort of code they stand on, because otherwise the choices don't make any sense. And I need them to. I do like a with some flair, some pizzazz, you know, panache, if you will. You know. So I like the little bit more flashy protagonists for sure. You know, Captain Kirk or, you know, Tony Stark, you know, somebody like that. I love those kind of protagonists, Don Draper, you know, but yeah, they don't again, they don't have to be like, well, I just have to want to watch them. I just have to find them entertaining. You know, I think that's what like, for example, that's what made Game of Thrones unique is that you didn't like most of the protagonists, but they were very entertaining.
+00:10:30 Darius
+Yeah, the that's the thing. they have to be engaging. They have to have good dialogue. Yeah, they just have to. I have to feel like they're not being propped up by like the writers behind the curtain. Yeah. And just, you know, that's one of the reasons, you know, Game of Thrones fell off or got a little worse in the later seasons is Jon Snow just developed insane pot armor and, you know, can't really have that. Have you ever had a show where you didn't like the protagonist but you still liked the show?
+00:11:10 Jordan
+Yeah. I'd say, I mean, I could go for like most teen dramas. So basically, Pretty Little Liars, Euphoria, Gossip Girl, any of those shows. You know, Boy Meets World. Corey was kind of insufferable. He was he was kind of a goody two-shoes know-it-all. He was a bit self-righteous. I always want Sean a bit more relatable. I'd say Big Bang Theory Sheldon is not likable. We just like him because the people in the show put up with him. So we feel bad for them. Transitively, we like them, like him, you know.
+00:11:53 Darius
+How much of that is that people think, I mean, Sheldon has some sort of clear Like developmental issues. Yeah. I don't know the right word to say and I want to have to edit this later. So I'll just say that he's right. The elevator doesn't know the top flow.
+00:12:08 Jordan
+Probably. Yeah, he's on a spectrum for sure. But I think even without that, I think he would have been an *******. I'm going to be honest. I think he was just an ******* who happened to have a developmental situation. I think who else? Who else? I'm trying to think. Sean from Psych, he was supposed to be immature. Like that's kind of the point of the, that's what drive the show. But the situation he put Gus in and the cops in by just like trying to go in guns a blazing, but literally with no gun, could be frustrating. You know, he'd be like, oh, I know you killed him. And they pull the gun and it's like, okay, well, that's why you don't tell them that because you know, you're not a cop. And he put Gus in bad situations too, because Gus would have to be the responsible one to make up for Sean's irresponsibility. So that can be frustrating to watch because you in real life, you would never do that to your friend and you wouldn't hang out with a friend who did that to you all the time.
+00:13:06 Darius
+Speaking of think that came on right after my example, the show suits. I hated Mike and I love the show. So I found Mike to be an entitled brat who did never showed proper appreciation for what Harvey did for him. He always wanted to use the firm's time to like do cases for poor people and ****. And it's like, dude.
+00:13:29 Jordan
+Yeah, he did. He did. This ain't that kind of law firm.
+00:13:34 Darius
+This ain't that kind of law firm. And ************ when I found you, was about to get arrested for selling weed to low lives in like, you know, I gave you, we don't just hire shot of shots. This is the most prestigious law firm in, you know, in this fictional New York City. And you're treating it like, I picked up your tab at Starbucks, it's not, I don't care that you are mission driven. You don't, doesn't matter, man. I just felt like he never, Harvey was remarkably patient given what he did for him. And he just, the whole time I'm watching the show, I'm just like, I don't understand how Mike doesn't see, it makes sense how Mike could be that smart. and be that unaccomplished because he's just, he doesn't get it. He's like watching the show, I could realize how he ended up in a predicament that he was in because he's incompetent. Like once he got into the show, you could see it. And it just, I guess it kind of makes it wouldn't make sense if he did it right.
+00:14:41 Jordan
+If he was just like Harvey. Yeah.
+00:14:42 Darius
+But yeah, watching it, because if you're just like Harvey, he'd have just went to Harvard and, you know, with his intellect and, but just watching it, got frustrating because I just felt like he never understood. the gravity opportunity that Harvey was giving him. So that's my example of a show where I didn't really like Walter White, Breaking Bad, but I love Breaking Bad. That's always out there. Good one. I love Dom Draper, even though by the end he was a mess.
+00:15:07 Jordan
+Yeah.
+00:15:09 Darius
+The Wire doesn't really have a protagonist.
+00:15:12 Jordan
+Right.
+00:15:12 Darius
+It's just everybody. Six Feet Under. I like that dude. I think those are all my Pantheon shows.
+00:15:21 Jordan
+Yeah, I mean, my favorite shows, Michael's, you know what, Michael Scott was a protagonist, but like, he wasn't always likable. That's actually, he's probably the most complicated protagonist in the history of American sitcoms, I'd say.
+00:15:37 Darius
+Michael Scott is the office, right?
+00:15:39 Jordan
+Yeah, because he could be super like, He had an extreme insecurity and people pleasing nature, but he also was very politically incorrect and could be a tool and, said sexist, racist thing sometimes, but you knew he didn't mean it, but so he was a pretty complicated protagonist and he could be hard to root for at times. Who else? Who have some of my favorite shows? Okay, so I'm rewatching once upon a time right now. It's a the concept of the show is basically you take all the storybook and fairy tale characters in history of like literature and they're in a universe and they get transported to the real world but they're cursed so they don't know who they are. And then eventually the curse is broken. And then they kind of just figure out their laps. Yeah. So it's like super dope. Like, and it has like a cool twist. So like, for example, like Red Riding Hood is a werewolf, you know, **** like that. It's really, really dope. And the main character is the child of Snow White and Prince Charming. And she's the child, the savior supposed to break the curse. But she's like traumatized because she was like abandoned because they had to they sent it through a portal to avoid the curse, basically, you know? And So she grew up with all these abandonment issues and stuff that she can't believe in anything. But when you're in a show where everything's built on these fantastical elements, the character who doesn't believe anything is just really, really frustrating sometimes. Even though you get why she doesn't believe in it because of the trauma of, you know, basically being raised as an orphan, you're like, bro, get it together.
+00:17:10 Darius
+What streamer is that one on?
+00:17:12 Jordan
+It's on Disney Plus.
+00:17:14 Darius
+Okay. Yeah, I don't have that one. And I am done paying for new streamers with sports coming up, but it sounds intriguing.
+00:17:22 Jordan
+It's dope. It's a really good show. It peaked after like season four, but it's a dope show.
+00:17:26 Darius
+It's, oh yeah, I'm out. That's too long. That's too much of A commitment for me to get into. But yeah, you got any other examples?
+00:17:39 Jordan
+You know what? I might catch some flack for this and I'm okay with that. Both the parents in good times. Okay, so here's why. Here's why. So James was stubborn as ****. And, you know, he's where the highway, but it's like, you know, my house rules and say, I get it. But your house is two feet tall. Like, he's up on the he's up on the misogyny, bro. Okay. And then also, like, not letting Florida work. We all in the hood and y'all are like half a check away from homelessness. That's crazy. Um, making these your brain.
+00:18:10 Darius
+Schemes when you're half a check away from homelessness.
+00:18:13 Jordan
+When they bought the encyclopedias and ****.
+00:18:18 Darius
+You don't really get to chase your dreams when you have a whole family to feed.
+00:18:22 Jordan
+No.
+00:18:22 Darius
+That's not, you gotta give that up when you got mouths to feed.
+00:18:26 Jordan
+Yeah, them not letting Florida work, but them making JJ work and using his money from his art to pay for them to take dance classes. Like, Doma gets a bed, the two boys are sharing a couch, JJ 62 in a plump couch.
+00:18:40 Darius
+Well, I mean, that was okay, but like that was fine. Like they didn't do that on purpose. They did that because they had. Well, I don't how. Yeah, I mean, that's true. They I don't not well versed in the good times universe to really give a much of A take on it, but it is a parent's job to provide and they were not meeting that obligation to say the least.
+00:19:08 Jordan
+Or whenever it be time for them to come into some real money, even if it maybe was not like the most ethical. I'm like, bro, you, I'm sorry. At this go out the window when you're in the projects. I'm sorry. That's just what it is, bro. You got three kids. **** them. **** the right and wrong. I'm sorry. I don't mean to. I'm not saying so drugs, but if you find them dogs on the road.
+00:19:25 Darius
+You might need to. These kids got to eat, man. I don't know what to tell you. Yeah, man. You're not making **** shake, but. No. Now I hear you, man. Do you want to get into the next topic? Yeah. So I'll be brief with the lead in because it's a bit wordy, but Chris Hayes, writer and cable news host, recently wrote a book called Sirens Call, and he has his take in there that I thought was pretty good and topical with Odyssey just coming out. And he's like, in the Odyssey, Odysseus is told you're about to travel through this area. And you're going to hear a sirens call from this woman that's so alluring, you're going to want to jump into the river and go after her. And he in Cersei instructs him to put wax in your crew's ears and tie yourself to the mast to keep yourself from following from heat from following the sirens call. And Chris Hayes has a take that basically modern siren calls are like our phone calling us for attention and the constant grabs at our attention and how our attention is monopolized and monetized today. And so you have to come up with ways to tie yourself to the mast to avoid falling for the trap of reaching for your phone. So my question to you is, what are some ways, what are some things you do to tie yourself to the mast when you need to focus or get something done?
+00:20:48 Jordan
+Something that I do to tie myself to the mass, so to speak, would be anything that just like allows me to think less or have to make less decisions so I can just focus on getting things done. So like sometimes I'll listen to the same song on a loop for like an hour or two. That way I'm not looking for another song to scroll and looking for another song. Then I get to, oh, let me go to Instagram. Let me go to Snapchat. Let me go to Twitter. Let me get, you know, so it's **** like that. Let me just play one song for an hour. And that way I can just throw my phone away and, focus on whatever I need to do. That's one thing I do. Or I'll use a playlist. Sometimes I'll just, I'll like sit in silence or, and I, but I have like a white noise machine where I can select different noises and then I'll throw on like an ambient screen on my YouTube for like they have these like random like ambient feeds that last like Anywhere from like 3 to 24 hours and you can just put on. So I'll put on one of those screens and then I'll just focus on editing or working or writing whatever task, reading whatever task I'm trying to fulfill. And then if I get really desperate and I just really need like a hard reset, I'll just take a shower. Like I could have taken a shower 2 hours ago and I will go and take another shower and act like I'm getting dressed. And I'll just, it's like a hard reset for me. That's kind of like how I just start the day over. If I have a rough day at work, I took a shower right at 5:00 and wash work, work off of me and just like, listen to some chill music and then I'll, you know, eat, game, whatever. And then I'll go back to trying to be an adult or something like that. But yeah, those are a few things that I do to try to try to clear my head and reset.
+00:22:24 Darius
+I have recently started to look for ways to get the information I need without my phone. So I recently subscribed to the Raleigh News and Observer, the actual print paper to be delivered. And so read the news on a physical piece of paper, which is wasteful and going to create a bunch of junk. But it's a way for me to get the local news. Also, I think the writing's better when it's in the actual paper. There's a style of writing for the internet that I find annoying because it's written for SEO reasons.
+00:22:59 Jordan
+Right, yeah.
+00:23:00 Darius
+And you don't get that in the actual paper. The writing is better. I'm thinking about getting a dumb phone, which is basically a cell phone that can just text and call. And I will probably install like YouTube music on it. And that'll be what I take to the gym so I can work out without being connected to the apps. And then I started so I lift Monday through Thursday, and then I go for a four miler on Friday and a two and a half miler on Saturday. And I've started Saturday, the two and a half miler to just no cell phone. And so I just like, just walk, you know, and it's hard at first. The 1st 10 minutes, you're constantly like looking for some stimulation, but you'd be surprised how quickly your brain just like resets. And just, you know, just trying to learn how to be bored again. And a lot of ideas come to me when I'm just on those walks. And I think you do have to remove a lot of the stimulus to get the creative juices flowing. Yeah, man, I just, the more, the more stuff I read on it, the more I can, the more time passes, the more I'm convinced that smartphones are cigarettes. And in 100 years, they're gonna, people are gonna look back on us with our phones in our hands. Like we look back on those pictures of people smoking in restaurants. Like I cannot believe that's how people lived. Like they really like sat there.
+00:24:29 Jordan
+Oh my God, they had smoke in here.
+00:24:30 Darius
+Yeah, like they just smoked on an airplane. And you know how we look at that? Like that's just insanity. Like they didn't know that they were killing themselves. That's how people will look at us staring at our phones all day. They're just going to be like, they did not know that they were literally I was scrolling Netflix last night because I just watched It was terrible. And I was like, let's see.
+00:24:54 Jordan
+Is that about the friends who swap moms?
+00:24:56 Darius
+Yeah, it's it was awful. Yeah, I watched that.
+00:24:57 Jordan
+I watched that ****. That **** was crazy.
+00:24:59 Darius
+Absolutely. Just terrible movie. And there was like a Netflix shorts. It was like 13 minute videos. It was like walking to Usher's home, walking to Kiki Wyatt's home. And I'm like, our attention spans are so short shot that Netflix has to do shorts now. Like we can't even watch slop for longer than 10 minutes. And yeah, man, I just, I can feel my attention span returning as I wean myself off. And I just think that the sirens call is really bad for us. And it's only, I just, I really, that's one of the things I'm I have my most conviction on is that 100 years from now, they will look back on photos of us out and about with our phones in our hands. Like we look back at people smoking cigarettes in public spaces. And so that's, those are the ways I do it, man. You got anything else for that topic?
+00:25:56 Jordan
+Yeah, I mean, for me, I found like the best way to research is finding quick ways to do it. Like, I'll literally like, game for like 10 minutes just to like, okay, let me just do something fun real quick and then get back to doing what I need to do. So I haven't lost an hour or two or whatever. That's one thing I do. Like I read, but sometimes I don't always have the attention to just lock in and read for an hour or two. And I found that for longer books, even though I'm reading it, I feel like I'm not getting anything done because I haven't finished it, if that makes sense. So I'll read like a few poems or something like that. And then that gives me makes me feel like I've accomplished something. And then that motivates me enough to get whatever else that I need to get done taken care of. So finding short, small tasks to build up to the big tasks.
+00:26:43 Darius
+Yeah, I you know, I struggle with that too. Like any book larger than 400 pages or like reading for more than 30 minutes at a time. But The more I get into it and the better I get at it, the more I think that those shortcuts just don't work. It's like lifting weights. You just have to lift the hard weights. So you have to sit there with that book. And even if you don't remember any of it, you got to look at it for an hour. And the next time you look at it for an hour, you'll pick up more of it. I just don't think the hacks work. I really don't. And so it's just like your brain is a muscle and your attention is a muscle. And you just sometimes have to strain. Sometimes you just have to lift that heavy weight and you got to strain it. It's going to suck and you're going to yawn a lot. But the second, the next time the weight's a little lighter. And, you know, I just think I think the people in general just need a little tough love about it. And no, you can't. You can't like hack your way out of it. You just got to lock in. And no, yeah, you can't. It was something about seeing that Netflix short where I was like, we really are just becoming dumber. Like, it was really a 13 minute video on Netflix because Netflix knows we can't watch something for, we can't watch an episode of a sitcom anymore. We have to watch a shortened version.
+00:28:03 Jordan
+Yeah, no, that's real. That's why even like Twitter does those ****** AI clips of movies where they have that ridiculous voiceover while the characters are speaking dialogue. You know, or even like, I know, like I was with family. at a dinner like a few weeks ago when we were talking about like how bad our attention spans have gotten and I was like man.
+00:28:24 Darius
+It's just funny though that like it took a long time and so and we it's like been like a 70 year but the moral panic over TVs riding our brains was actually right They were right all along.
+00:28:42 Jordan
+They were, they were right. They were just 100 years too early.
+00:28:45 Darius
+Yeah, but they're right. But it's like, it's funny though, is like getting older is realizing like a lot of like the social panic over like 90s trends, like Actually, violent rap music isn't probably a good idea for young men to listen to. Actually, drill music has not been good, and they probably should not be listening to that stuff. You know, **** is probably really bad for people. We probably should not, like, you know, TV's bad for YouTube. Like, they were right. We just need to be like, hey, you know what? We were, we were, you were right. You know, when C Delores Tucker told Tupac he was being disrespectful to women, she was right.
+00:29:28 Jordan
+And when Michelle Obama tried to get us to eat vegetables, we hated her for it, but she was right.
+00:29:33 Darius
+You know, like, I think the boomers.
+00:29:36 Jordan
+And look at us now we have no FDA and they're trying to kill us all.
+00:29:39 Darius
+You know, the boomers had some points and you know, I've lived long enough to see a lot of the 90s moral panics actually turn out to be true. So, you know, listen to the elders. Sometimes they have some points.
+00:29:52 Jordan
+That's a good point.
+00:29:52 Darius
+You want to get into the next topic.
+00:29:55 Jordan
+Yeah. I don't remember even how I came up with this, but I was thinking about a honorable. So I was reflecting on this year and this year's been kind of tough and it has not really gone the way I thought it was going to go or had wanted it to go, at least thus far. So it got me to thinking like, I didn't want to get down on myself because I haven't accomplished or certain things hadn't happened the way I wanted them to happen this year. So I was like, okay, I got to focus on like what I want to happen for the next four months. Like what things do I have to look forward to? So I can kind of build on that towards next year, basically. So I'm thinking, what are some things that you're looking forward to or benchmarks you've said or just like a movie release you're excited for, you know, a book coming out you're excited for, something like that.
+00:30:42 Darius
+Well, before it was Madden. And so I did not play Madden for like 10 years because it was just, I thought it was stagnant and it wasn't doing anything. And something that I've said before on here is that You can't complain about something and keep buying it because you're not, how are you signaling your displeasure? And so I stopped buying it and I got back into it last year and it's good now and I enjoy it and it's fun. And so that was something I was looking forward to. Currently looking forward to football season. That's kind of my time to shine. Just bought a new TV to add to the system and really looking forward to having my weekends programmed for me. Yeah. I just. That would be movies. See, the thing is, my big release was Odyssey, right? And so now I'm getting back into the groove of just like seeing the random things that I always like. I got we reviewed the drama. I don't know when it's going to release, but like. I saw that at home and that's something that I would have went back into the movie theaters and saw, but I'm going to try to get back into going to the theaters. But things to look forward to, man. Looking forward to season two of this pod. I'm looking forward to, you know, getting our getting back into a full production schedule. I'm looking forward to writing a little bit more and just I think the fall, the fall brings more structure to like everything. And so it helps you, it makes me more productive, which sounds crazy because, there's a lot more on TV, things that can distract you, but I get more productive in the fall. Because the summer is just, there's a, there's a leisure nature, leisurely nature to the summer that can, you know, consume you if you let it. So I'm looking forward to the, I've this, I've been lifting for about a lot, I've been lifting forever, but the last month I've been kind of injury free. And so I've been ramping up. Just really locking back in on the fitness kick and looking for, seeing the charts go back up is good. Okay. Yeah, just, trying to get more juice out of the squeeze of the day-to-day instead of just kind of, I'm just trying to attack more days, you know. How about you?
+00:33:09 Jordan
+It's funny you brought up Madden. I actually was talking about Madden at the barbershop on Saturday with our barber. And he was like, I was like, bro, this **** is</t>
   </si>
 </sst>
 </file>
@@ -8655,6 +10130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8678,7 +10154,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>107</v>
       </c>
@@ -8692,7 +10168,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>108</v>
       </c>
@@ -8706,7 +10182,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>109</v>
       </c>
@@ -8720,7 +10196,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>110</v>
       </c>
@@ -8734,7 +10210,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>111</v>
       </c>
@@ -8748,7 +10224,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>112</v>
       </c>
@@ -8762,7 +10238,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -8776,7 +10252,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -8790,7 +10266,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>115</v>
       </c>
@@ -8804,7 +10280,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>116</v>
       </c>
@@ -8818,7 +10294,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>117</v>
       </c>
@@ -8832,7 +10308,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>118</v>
       </c>
@@ -8846,7 +10322,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>119</v>
       </c>
@@ -8860,7 +10336,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>120</v>
       </c>
@@ -8874,7 +10350,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>121</v>
       </c>
@@ -8888,7 +10364,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>122</v>
       </c>
@@ -8902,7 +10378,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -8916,7 +10392,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>124</v>
       </c>
@@ -8930,7 +10406,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -8944,7 +10420,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>126</v>
       </c>
@@ -8958,7 +10434,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>127</v>
       </c>
@@ -8972,7 +10448,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>128</v>
       </c>
@@ -8986,7 +10462,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>129</v>
       </c>
@@ -9000,7 +10476,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -9014,7 +10490,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>131</v>
       </c>
@@ -9028,7 +10504,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>132</v>
       </c>
@@ -9042,7 +10518,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>133</v>
       </c>
@@ -9056,7 +10532,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>134</v>
       </c>
@@ -9070,7 +10546,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>135</v>
       </c>
@@ -9084,7 +10560,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>136</v>
       </c>
@@ -9098,7 +10574,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>137</v>
       </c>
@@ -9112,7 +10588,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>138</v>
       </c>
@@ -9126,7 +10602,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>139</v>
       </c>
@@ -9140,7 +10616,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>140</v>
       </c>
@@ -9154,7 +10630,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>141</v>
       </c>
@@ -9164,8 +10640,11 @@
       <c r="C36" t="s">
         <v>37</v>
       </c>
+      <c r="D36" s="3" t="s">
+        <v>257</v>
+      </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>142</v>
       </c>
@@ -9175,8 +10654,11 @@
       <c r="C37" t="s">
         <v>38</v>
       </c>
+      <c r="D37" s="3" t="s">
+        <v>258</v>
+      </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -9186,8 +10668,11 @@
       <c r="C38" t="s">
         <v>39</v>
       </c>
+      <c r="D38" s="3" t="s">
+        <v>260</v>
+      </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>144</v>
       </c>
@@ -9197,8 +10682,11 @@
       <c r="C39" t="s">
         <v>40</v>
       </c>
+      <c r="D39" s="3" t="s">
+        <v>261</v>
+      </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>145</v>
       </c>
@@ -9208,8 +10696,16 @@
       <c r="C40" t="s">
         <v>41</v>
       </c>
+      <c r="D40" s="3" t="s">
+        <v>259</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D40" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
+    <filterColumn colId="3">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D7E547-9628-4C5F-8E3F-857AB0BD8698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE37E48-003A-4107-AB1F-4D2DCBCFB419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="266">
   <si>
     <t>youtube_link</t>
   </si>
@@ -9001,6 +9001,339 @@
 00:33:09 Jordan
 It's funny you brought up Madden. I actually was talking about Madden at the barbershop on Saturday with our barber. And he was like, I was like, bro, this **** is</t>
   </si>
+  <si>
+    <t>09.08.26</t>
+  </si>
+  <si>
+    <t>Topics Covered
+• DaBaby's Charlotte food truck, IG restaurant culture, and whether any food is worth a three-hour wait 
+• Funny childhood decisions that probably terrified their parents 
+• Running away as a joke, dangerous sledding, trampoline stunts, stair surfing, and neighborhood mischief 
+• Family traditions that are disappearing and who is responsible for preserving them 
+• Millennials inheriting the responsibilities once handled by parents, grandparents, aunts, and uncles 
+• Analysis paralysis versus taking action and building momentum through consistency 
+• Podcasting, audience-building, and becoming part of someone's routine 
+• Posting content online, social media anxiety, and worrying about public judgment 
+• Whether hobbies should become businesses or sources of income 
+• Influencer culture, authenticity, and the dangers of turning everything into content 
+Best Questions
+• Is there any restaurant worth standing in line three hours to eat at? 
+• What is the funniest thing you did as a child that terrified your parents? 
+• Which family traditions are actually worth preserving? 
+• Why do talented people get stuck while less-talented people succeed? 
+• Should hobbies be monetized? 
+• At what point does content creation stop being fun and start becoming work?
+Best Observations
+• Many traditions disappear not because older generations stop caring, but because younger generations never pick up the baton. 
+• Consistency often beats talent because people become part of their audience's routine. 
+• Most creators are terrible judges of what audiences will actually connect with. 
+• An unfinished project seen by people is usually more valuable than a perfect project that never leaves the hard drive. 
+• Social media rewards authenticity but simultaneously pressures creators toward performance. 
+• Many hobbies become less enjoyable when every moment is optimized for engagement and monetization. 
+Best Debate
+Should Hobbies Make Money?
+Jordan argued that there is nothing wrong with earning money from something you already love doing and that monetization can be a blessing when it happens naturally. Darius countered that commercialization can slowly drain enjoyment from a hobby and pointed to influencers who clearly no longer enjoy the content they create but continue because it has become their job.
+Themes
+• Childhood memories
+• Family traditions
+• Adulthood
+• Community responsibility
+• Consistency
+• Creativity
+• Podcasting
+• Social media
+• Content creation
+• Monetization
+• Influencer culture</t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:00 Darius
+We have to grab the baton. Traditions are dying out because we keep expecting the grownups to do it. But we're the grownups.
+00:00:06 Jordan
+Keep doing it. Yeah. No, that's not the grownups.
+00:00:09 Darius
+That's Jordan. Welcome to Out the Trunk with Jordan and Darius. My name is Darius. That's the use all up in area on all socials.
+00:00:15 Jordan
+And I'm Jordan. That's Jordan to be writing on all socials.
+00:00:18 Darius
+This is our segment, our weekly segment. We titled What's On Our Mind, where we let you guys know what's on our mind. Starting off, North Carolina's own Da Baby has opened up a newer restaurant in our sister city, Charlotte. And have you seen the menu yet?
+00:00:36 Jordan
+Yeah, I did. I did see the menu. I'd heard about the prices on Twitter. I mean, I figured the price would be a bit whatever you want to average you want to use because it's a rapper doing a food truck. But honestly, they weren't they weren't as crazy. I thought they were going to be like the 40 bucks for the waffles or whatever the combo was kind of crazy. But other than that, the prices weren't that different from regular food trucks from what I see.
+00:01:01 Darius
+Yeah, you know, I will put the menu up there for the viewers and listeners. I must say I find the actual pricing on the waffles to be insane, but the rest of the menu looks like a regular restaurant.
+00:01:13 Jordan
+Yeah, everything else is pretty normal.
+00:01:16 Darius
+I'm not sure what a seafood boiled egg roll is. I don't know what's going on.
+00:01:21 Jordan
+I don't know what the hell. That tastes like. That sounds like diarrhea in a basket. I don't know what that is. I feel like you'd be printing to the porcelain princess after a couple of those.
+00:01:33 Darius
+Yeah, I'm down with those.
+00:01:36 Jordan
+I'm ******* with it.
+00:01:39 Darius
+I just can't see myself ever paying $25 for a waffle. Not for one waffle.
+00:01:45 Jordan
+No, that's, you know what it is? It's funny because he's from Charlotte, basically.
+00:01:51 Darius
+Yeah.
+00:01:51 Jordan
+He lived in Cleveland for a little bit, but he's from Charlotte, went to UNCG. And people from North Carolina, we always say, Charlotte wants to be Atlanta so bad. And those are Atlanta *** prices.
+00:02:04 Darius
+It's just, it apparently people waited in line like 3 hours.
+00:02:10 Jordan
+I saw the pictures. Yeah. The videos. Yeah.
+00:02:13 Darius
+What on this menu would you ever? I don't get it.
+00:02:19 Jordan
+Yeah. I mean, The egg rolls are good. I mean, the price for the egg rolls is actually, you know what? I take it back. The price for egg rolls is 20 bucks for egg rolls is crazy. Unless it comes with like 5. Yeah, I mean, the lobster and grits seems pretty good. I'm sure the crab fried rice is good. Can't go wrong with fried fish.
+00:02:36 Darius
+Is there any restaurant you would stand in line 3 hours to eat at?
+00:02:39 Jordan
+Dude, I don't think there's a movie I stand in line for three hours.
+00:02:43 Darius
+You know, if it's like a take your number, we'll text you and your table's ready. You can go around. Okay, I can make that work. They can go home and watch a movie, you can go shopping, you can go, whatever. But actually physically standing in line, I don't think there's any restaurant on earth that would do that for.
+00:02:58 Jordan
+Yeah, I don't, yeah, no. Unless like, if like Rihanna was divorced and was like there, maybe.
+00:03:09 Darius
+Is it really just because there's nothing on this menu you haven't had before? No. Even if it's great. Like if you've had a chicken wing, you've had a chicken wing. If you had fish.
+00:03:17 Jordan
+If you had waffles, you've had waffles.
+00:03:19 Darius
+What are you waiting through? What unique experience are you waiting 3 hours to have?
+00:03:22 Jordan
+I think that's one of those things you just went to say you went like that's really, I think what it is. It's so you can say I went there and give a review or some ****. Like if Keith Lee went there and waited 3 hours, I'd be like, okay, I get it because like that's what you do for work.
+00:03:35 Darius
+Yeah.
+00:03:37 Jordan
+I don't understand. I mean, props to him, congrats to him, sport black businesses, but three hour wait is nuts.
+00:03:46 Darius
+We're trying to plan a trip down to Charlotte to catch a Hornets game. Is this going to be on the itinerary for you?
+00:03:53 Jordan
+If the line ain't crazy, I'm down to go. If the line is not crazy, I'm down to go. Otherwise, you know, I'll be airdropping my support.
+00:04:02 Darius
+Absolutely not. I don't do IG restaurants. This is this menu looks like it was just. The only thing it's missing is jerk lamb chops and salmon bites. And it's just straight out of an IG, flower wall restaurant menu.
+00:04:18 Jordan
+Yeah, it's very content wall coded.
+00:04:20 Darius
+Yeah, and it's just, I don't like those restaurants because like, I just have a rule of thumb, generally speaking. If I go into the restaurant and there's a DJ, I'm out. I know the food is not the focus if there's a DJ in the spot.
+00:04:34 Jordan
+Well, that's fair. I'm not mad at that take.
+00:04:37 Darius
+It's a day party with waffles and chicken.
+00:04:40 Jordan
+Right. Yeah, it's really just a day party with like food so you don't die. But it's funny because looking at the menu, it remember at the bar, I think Sunday, and there was that video of the fried fish with the pound cake as like the bread, fried fish. And I feel like that would fit with that food truck. Like that's like the overall kind of lab I get.
+00:05:02 Darius
+I ain't going to hold you though.
+00:05:04 Jordan
+That pound cake pound fish kind of look like ****. Listen. Would I get diabetes from it? Sure. Would I want a slice? Yes.
+00:05:13 Darius
+I would probably take the top piece off and just have one piece of the cake in the fish. Yeah. And could I eat it all in one sitting? No. But like we said, I don't think it's materially different than chicken and waffles.
+00:05:25 Jordan
+No, it's not.
+00:05:26 Darius
+It's a fried protein and a savory pastry.
+00:05:29 Jordan
+And a breakfast.
+00:05:30 Darius
+I mean, a sweet pastry. You know, like it's.
+00:05:33 Jordan
+I mean, it's basically, you know, a black arepa.
+00:05:36 Darius
+Yeah. It's not as like offensive as like when they put like Lemon pepper on the martinis or whatever. Yeah. Like, that's actually a pound cake fried fish while, should not be in your regular rotation because we wanted to be on this earth a long time. For sure. When in Rome, I would try it. I would try that.
+00:05:55 Jordan
+Yeah. When in Atlanta or wherever it was at, he'd try it.
+00:05:59 Darius
+But everything else on this menu, I just don't see myself. I'm sure the food is fine, pleasant, whatever, but I just, I'm not, this isn't really my scene. I'm more mom and pop. Locals know the spot. Like any rapper restaurants, probably just not gonna be for me, generally speaking.
+00:06:19 Jordan
+So. no Wingstop then.
+00:06:21 Darius
+Hell no. Wingstop's terrible. Wingstop is trash.
+00:06:26 Jordan
+Jessica, it is technically a rapper restaurant.
+00:06:30 Darius
+Yeah, I don't.
+00:06:31 Jordan
+Shout out Rick Ross.
+00:06:32 Darius
+Yeah, but like. I'm not willing, like I've seen pictures of the food from the baby's restaurant and I'm sure it's pleasant.
+00:06:40 Jordan
+It actually looks good. Yeah.
+00:06:42 Darius
+Wingstop is just nasty. Like it's not pleasant. It's just, it's a, it's worse. I'm worse for having gone there.
+00:06:52 Jordan
+All the wings are fried hard.
+00:06:55 Darius
+Cheese fries is just like that goo that comes with new movie theater nachos. Anyways, want to get into your first topic.
+00:07:06 Jordan
+So I saw a viral TikTok and the trend was, or the caption was, the scariest things you did as a child, sorry, funniest things you did as a child that scared your parents to death. So I thought I have a couple instances. I remember me and my brother and my sister, we were sledding one year in the woods. It was like a big like slope we were going down. And so we went down there and we saw, we like noticed there was like a cinder block that was like lodged underneath the snow. And we, I screamed it out and I guess my brother didn't hear me or didn't jump off in time. So we all jumped off the sled and he went airborne and he like cut himself on some thorns.
+00:07:46 Darius
+Okay.
+00:07:47 Jordan
+That was one. Also the backstory is we were like, oh, let's go sledding. Let's do the woods because it's a bigger slope. It'd be more fun. We can get some air. And I asked my sister to go ask my mom if it was okay. She was like, okay, cool, I'll do it. We didn't know that she actually didn't do that. And we weren't supposed to be doing that. So we go back to the house up the hill and we're like, hey, so we went sledding and Brandon cut himself on some thorns. And he's like bleeding. And my mom's like, what the hell? Who said y'all could do that? So that's one. Another one is I pretended to run away, like as a joke. I wasn't actually running away. And I didn't have a watch since I was a kid. So I'm just hiding in between like some neighbor's yards or whatever, like up the street. And I just lost track of time, I guess. So it was the point where like they thought I actually was missing. So like, I'm walking down the hill back home and my mom's like, about to cry. She's like, Oh my God, y'all just wait here. I'm going to go driver. I'm looking for him. If I'm not back in 15 minutes, just call 911 and tell me your brother's missing. And I kind of walk up like, Hey, guys, I'm back.
+00:08:54 Darius
+How old were you?
+00:08:57 Jordan
+That one actually was old enough to know better. I think I was like 13.
+00:09:01 Darius
+Okay.
+00:09:03 Jordan
+And they beat the hell out of me.
+00:09:09 Darius
+That's, you don't do that, kids. Oh, no, kids. Don't run away. Well, yeah, that's true.
+00:09:15 Jordan
+If you are, turn this **** off.
+00:09:16 Darius
+Yes, please. For me, a little bit tamer. We once put the sprinkler underneath the trampoline. And I think they saw the medical bills flash before their eyes. And we would jump from the tree Onto the trampoline, sprinkler underneath, which, if I were to be like on a run and see some kids doing that today, I might be like, those parents are neglecting. Yeah, right, Where are they? I wouldn't.
+00:09:52 Jordan
+Where are the adults in the room?
+00:09:54 Darius
+That was wild.
+00:09:55 Jordan
+Yeah.
+00:09:56 Darius
+I once used the printer scanner to scan some money and that my mom thought the ******* FBI was going to knock on the door. She really felt like the feds were listening and she was... It is standard teenage stuff. I once went, I once lied about hanging out at a friend's house that was in the neighborhood. And we caught me and two friends. I haven't actually talked to them in a while, but I should. We caught the city bus over to the bad neighborhood to meet some girls. And we were, **** middle school, so I'd have been 8th grade. So whatever 8th grade is.
+00:10:37 Jordan
+12, 13. Yeah.
+00:10:39 Darius
+And so, the power of teenage boy ***** we caught the city bus all over, all the way over to bad neighborhoods at like 11 o'clock at night. And we just were missed teenagers. meeting some girls on the wrong side of the tracks. And, my parents kind of caught wind of it and picked me up at like 1230 at night. I was like 13 years old in a terrible neighborhood at some girl's house at 1230 at night. So I don't know if it was funny, but it was it was fun. It was fun.
+00:11:12 Jordan
+And it definitely terrified me.
+00:11:13 Darius
+So I don't know if I followed the rules there, but those are my three.
+00:11:16 Jordan
+No, that's good. So I had to read it. I got to read a couple of the comments in the thread because they're so insane. One kid said, My mom was driving on the freeway and I covered her eyes from behind and said, guess who? That's so bad.
+00:11:33 Darius
+Okay.
+00:11:35 Jordan
+I don't know what possesses me. I mean, I know kids do **** **** but like while driving is pretty insane. Let's see if I can find another one. Oh, the kid said they were waiting across the street and the kid was like, I bet I can go straight before this car hits me and just like took off running.
+00:11:54 Darius
+We used to there was a train tracks behind our house and me and my neighborhood friend Kyle's and Kyle and Corvin, we would throw rocks from the train tracks at cars. Just mischievous youth. I don't think you ever hit anybody because it's actually really hard to hit a moving car with a rock from a bridge. But we thought we thought it was just like, playing target practice, but the movies. but it's actually pretty difficult to do. And we I don't think we ever actually hit anything, but that's good. some other neighborhood mischievous kid things that I'll just say for the memoir.
+00:12:39 Jordan
+Yeah, we used to play in this like lake that was in our neighborhood. Looking back, I'm pretty sure it was like not clean water. And there was like a tunnel to the lake, but I think it was just like plumbing. So I think again, it was not clean water that we were playing in. And we came home covered in mud and our parents, we couldn't play. None of us played outside for like a week or two after that.
+00:13:01 Darius
+I remember one time I had some brand new Tims and I, you know, I was a kid, so I wasn't really up on the science of it, but they had, I stepped in a puddle and I thought like the water was permanent. And so, I'm freaking out 'cause them was like, those are hundred-something dollar shoes, and this is 90s money or early 2000s money when $100 was actually money, and like... the relief when like hours later it went away. Oh, because I thought that was the permanent because I didn't know it was just water. But like, it's like throwing water on a shirt. Eventually it dries out. And I didn't know that at the time. And you know, for a kid, you have no perception of time. So like that hour probably took felt like 3 days.
+00:13:44 Jordan
+And so no, yeah, for sure. Yeah, I definitely made the mistake of playing outside in my school clothes, in my school shoes. like the first day of school. Because my thinking was, well, my friends had different classes and I need them to see my shoes because as a kid, your friends need to see your shoes, your new shoes. But it wasn't worth the ******* when I got that. And I couldn't wear the shoes for like two weeks.
+00:14:06 Darius
+In seventh grade, I lost a couple of PlayStation one game shooting dice. That was not a good conversation. You know, I was at a cousin's house just shooting dice. And that was my currency. I had no money. So I'm like, how much bargain could I get with this spiral? And they were like 10 bucks. And I lost that **** so fast. It was a couple other, some games I didn't really care about. But yeah, man, I would burn CDs that people wanted and then go to like a cousin's house and he was at his currency to shoot dice with. Cause I'm the kid from the suburbs, right? And so my cousins and them, they were not in the suburbs. And so that's where we went, that's where I went to shoot some dice. And I ain't got no money. So we would burn, I would burn CDs, big CDs, whatever, things I knew people would like and be like, can I get in the game? I got Twisted and the Speed Snot Monsters. I got, you know, this Jay-Z album. And you know, cause I was like, So I could go on Napster and find the whole albums and make **** shake that way. And that's how I bought my way into dice games.
+00:15:18 Jordan
+So that's interesting. I did not get well as a kid, dude. Not that I can remember.
+00:15:24 Darius
+I mean, yeah, I love that. Yeah, shooting dice, playing spades. And eventually you graduate to poker, but that was like informal card rooms and home games and things like that. But no, man, I started, I was like 6th or 7th grade. You know, you drop your drop off at your cousin's house and, they shooting dice in the back room, like, let me get in. And, I was probably too young, but, older cousins, OGs, uncles, they like, this little dude can play. And, you know, like, so lost all my money and my burn CDs and my PS1 games. You got anything else for that one?
+00:16:09 Jordan
+Stupid **** I did as a kid. I mean, like a lot of, my brother broke a lot of furniture. We broke a drywall once fighting. So actually, okay, here's a good. So me and brother, we used to play this game. We used to play like dodgeball, but with pillows, but we would do it like we're like, The person dodging had to keep their eyes closed.
+00:16:29 Darius
+Yeah.
+00:16:30 Jordan
+So we were just chucking, and we broke a couple outlets and made a couple of dents in some walls doing that.
+00:16:38 Darius
+I once broke a vase in the living room, throwing a football around. And my **** *** thought if I just turned the broken part toward the inside, no one would put it. Actually, I think it bought me like 2 weeks because how often do you flip a race around?
+00:16:54 Jordan
+It's really about buying time when you're a kid.
+00:16:56 Darius
+Yeah, it was like 2 weeks might as well be next year, And so eventually I had to cop to it because again, someone's gonna look soon. But yeah, I like swept up the particles and spun it around and you know, it got me about two weeks of bail. So what do you do?
+00:17:12 Jordan
+I remember during the summer breaks, we do crazy ****. Like we have a banister, so we were like, I was like, I wonder if we could, I bet I could jump off the banister and survive, whatever, make it. And we're like, well, it's wood, so we don't want to hurt ourselves. So we took all the cushions off the couch and made a big pile of them on the foyer to jump off of. And then we were like, you know what? This might be a bad idea. So the second we put the last cushion back on the couch, our dad walks in the house and he came home early for that day, thank the Lord, that we came to our sentences. Did you ever do stair surfing?
+00:17:45 Darius
+With the mattress on the stairs or with the laundry mattress?
+00:17:49 Jordan
+We do it without the mattress. We would just put winter coats on backwards and just like dive down the stairs. Or we would take like cardboard and like fold it and then use that as like a sled.
+00:18:02 Darius
+No, it didn't do that. We actually used to sled down. I mean, because Minnesota, we had snow. And so we'd go sledding with no protective gear on steep hills. And it's a wonder that I like didn't break my vertebrae or something.
+00:18:17 Jordan
+Yeah.
+00:18:17 Darius
+Speaking of, we had a shed in the backyard. And so we would, it was about, I would say 6 feet off the ground. It wasn't like basketball height. And so we would climb that shed. We would rake all the leaves, put them in a pile and climb that shed and jump off into the leaves. So, just kids being outside, just you had to get out the house. So when you weren't going to sit in the house all day, especially during the summer. So, you had to we have a million different things to do. So we just made them games in the neighborhood, 21, 500, jumping off the shed into leaves, water, water under the trampoline, just whatever we could find to kill time, human ingenuity, baby.
+00:19:03 Jordan
+Pretty much, yep. What you got for the next topic?
+00:19:09 Darius
+All right, we got just a general prompt. What family traditions are worth keeping?
+00:19:21 Jordan
+So for us, we have, it's weird because like some of them don't exist anymore because like the people who have held them like passed away. So I'm getting there.
+00:19:30 Darius
+There's no point.
+00:19:31 Jordan
+Yeah, I think The first one I can think of that we still do regularly is every Christmas Eve, we always watch Twas the Night Before Christmas together as a family. We'll do like the eggnog and the hot chocolate and the cookies and all that stuff. You know, we still have it on V. We lost the VHS. We used to always watch it on VHS no matter what year it was, but we lost it. Now we just watch it on YouTube. That's one for sure.
+00:19:53 Darius
+You can buy it off of eBay, a new VHS.
+00:19:55 Jordan
+Oh, yeah, true. It's probably like 10 bucks.
+00:19:59 Darius
+I don't know about that, but if it's out of circulation, it could be priced, but
+00:20:04 Jordan
+you could probably find it. Yeah, that's one for sure that we always make sure to keep up with. Yeah, honestly, yeah, the rest of them kind of fell by the wayside, to be honest with you. Like we used to do like New Year's Day and New Year's Eve, like all together as a family, but like when, you know, certain grandparents passed away, it seemed like that kind of went with them.
+00:20:25 Darius
+I'm getting there. So this, I put this on here because Labor Day was recently. And I go through on this rant just about every time there's a holiday. You see a bunch of people, millennials, what happened to the cookouts? What happened to the traditions? What happened to this? And I need y'all to understand it's our job to grab the baton now. How old did y'all think your aunties and uncles were when you were a kid? They were our age. You 36 still trying to show up with soda and cups. and eat and get drunk and leave. And you wonder why, big mama tired. You need to get your *** on the grill. You need to bring, you stop trying to, you're too grown to try to show up with chips.
+00:21:06 Jordan
+Yeah.
+00:21:06 Darius
+Make a side, season some meat, offer people rides, put some money on something, grill something. It's our, we're supposed to be throwing the cookouts. It's our job to hold the family traditions and we're letting them die out because we don't want to go up. We still want to show up with a bottle of liquor and red solo cups and act like that's contributing to the function. And it's not. It's not. It is Big Mama and them tired. Don't nobody. She's 70 years old. She's not trying to pour over, make macaroni and cheese and grill.
+00:21:38 Jordan
+She looked like that last night now.
+00:21:41 Darius
+We need to. It's time to retire them and let them show up. Chips and pop and soda and ****. That's for college kids. That's what you bring. Hey, you bring paper plates because you're in college and you're 37. You can't show up to the cookout with paper plates anymore.
+00:22:00 Jordan
+With ice.
+00:22:02 Darius
+It's not okay. If it ain't nothing, but if you can't, everybody does different things. Show up early, help set up. Or even just put $50 on the meat. You know how much **** costs. You grocery shop. You know you can't go nowhere and spend less than $40 at no restaurant. So put some real money. $10 ain't no real money on the food. real money on it if you can't do anything just we have to grab the baton traditions are dying out because we keep expecting the grownups to do it but we keep.
+00:22:31 Jordan
+Doing it yeah yeah no that's.
+00:22:34 Darius
+That's true I just really wanted to set that one up so um that's it that's the only thing Labor Day that that gets under my skin so.
+00:22:43 Jordan
+Yeah sorry for I never thought about it no you're good no we never I don't know if we ever Yeah, Labor Day was never really a big thing in my family, honestly. Like, I don't think, nothing I can think of. I mean, Fourth of July, every once in a while, but even then that was kind of more of a casual thing. There's really just the big ones of Thanksgiving, Easter, Christmas for us, for the most part. Maybe New Year's every once in a while. We do friends, cousins giving now too, sometimes.
+00:23:08 Darius
+Even Thanksgiving, man. I understand that's a harder one to take from Big Mama, but She needs help. She wants help. It's like cooking for 30 people is not easy. And her knees hurt. Help her out, man. Hey, big mama. This year, I'm going to do the Macro.
+00:23:27 Jordan
+Y'all ruin the family.
+00:23:28 Darius
+For real. Like, hey, man, one of my proudest moments as a grown up, when my mom retired, May 2024. We threw her a cookout and I took grilling duties from my pops first time in my life. Like he just, I got to let him rest and I manned up. grill for the whole family. And that's like a seminal moment in a black man's development. And yeah, it's time. It's time. It's like, get on the grill. Season to me. If you got you got 50 chicken wings, help season them.
+00:24:04 Jordan
+Yeah.
+00:24:05 Darius
+It's something you can do. Stop showing up an hour late with a bottle of liquor. Like that's not enough anymore. It's not enough. We it's time. We're the grownups now. So anything else for that one?
+00:24:23 Jordan
+No, I think that's I think you pretty much covered it. That's all I got for that.
+00:24:26 Darius
+All right, Ben. Analysis paralysis. What you got?
+00:24:34 Jordan
+Yeah, so I was on TikTok and I saw this video of this guy. He was saying an idiot in motion is better than essentially a genius stalled out. Pretty much like he was saying, you know, sometimes people are successful not because they're more talented or more intelligent. They just have the audacity to put it out or to make something, you know, make something slash make something happen, you know? And, you know, he was talking about just like the importance of volume, like quality is cool and important, but quantity matters too. And it's about just like writing whatever you're doing. If you cook cooking on a regular basis, posting pictures of your food, you know, like doing the things that feel scary to you, until they're no longer scary. So I thought that was an interesting perspective on that.
+00:25:19 Darius
+There's a substack writer I follow and he made this great point and he's like, he sticks to a schedule of publishing, even if he doesn't think it's great. Because if you publish consistently, consistently, you're not relying on hits as much. Right. And so Yeah, he's like, I publish on Mondays, Wednesdays and Fridays, even if I don't think it's my best, because if I only publish when it's my best, it has to be my best. And so like you, if you, keep stuff out there and you honestly, half the time you don't even know what's going to resonate with the people the most.
+00:25:53 Jordan
+Right.
+00:25:54 Darius
+A lot of artists will tell you they hate their hit songs and they didn't even want like they had to be dragged into releasing it. And so often you're the worst judge of what is going to resonate with the people. So 100% man. with this pod, we release Mondays and Fridays, and it's just like consistently. And that's, that puts us ahead of the game. A lot of pod, I can't tell you how frustrating it is. Like there's a pod I listen to the press box with Brian Curtis and Joel Anderson and another guy, I forget his name, but ain't no telling when that ************ will hit my feed, man. Sometimes it's Tuesday morning, sometimes it's Monday afternoon. Sometimes it's like, It makes it's very frustrating as a consumer to just not be able to do the routine around when this pot and don't get me wrong. I don't expect to be at the same time, but like, can we get the day right? You know, it's like, especially on like office days. It's like, if it doesn't hit my feet before I leave the office, I'm not listening to it until the next day. And then by then it might be buried under what comes out from the next day. Correct. You're what I listen to on Wednesday. And so if you don't get it to me before Wednesday ends, now you're behind my Thursday priorities. And so you might, I've seen it where you just lost that whole week and I just pick up on you the next week.
+00:27:12 Jordan
+They fall into rotation.
+00:27:14 Darius
+Yeah, it's just people, you know, it's, I remember, you know, the, this is, maybe you have to be part of people's routines. A lot of the restaurants you frequent aren't even all that good. They're just on your way home from work.
+00:27:31 Jordan
+Yeah, literally, yeah.
+00:27:32 Darius
+And so I know people back in Minnesota who there was like, there was construction on Highway 100 on the exit that led to their restaurant. And he's just like, even when the construction was done, they didn't recover. And I was like, why? And he was like, people found new things to eat. You know, like, you know, if you're not on the exit, they can't take the exit to go to your place and go home and take a new exit. And they'll find new, they'll find a new routine. And so it has nothing to do with, I just was no longer in their vision. And how many times have you seen someone from the bar that we frequent buy a house 30 minutes away and they fall off the face?
+00:28:08 Jordan
+And you don't see.
+00:28:09 Darius
+And it's why, because it's no longer on the way home. It's no longer in their neighborhood. And it's like, oh, and it's you have good intentions. Oh, I'm still going to come by or da da da. You're not because it's no longer in your a part of your routine. And so, yeah, stay in people's routine, keep releasing, have some quality standards, but if you only release hits, they have to be hits, you know?
+00:28:36 Jordan
+Yeah, it's it gets challenging because it's like, but it does. It does. It is important because I saw this when I was I was doing research stuff for the pod and like how to get better and all that kind of thing. I saw this thing that said, literally, if you post, if you have a podcast and it has more than 10 episodes, you're literally automatically in the 1% because they don't make it past 10 episodes. You know, like there are things people want to do and they say they like, oh, this seems fun, it seems cool. And then they just kind of, you know, fall off the face of the earth with it. They don't, they don't stick with it. And like I really found it like that consistency really is important. Like it really is key. It sounds cliche and **** but it's really like, I've gotten noticed and opportunities at **** just because people know I'll show up. And people know like I'm gonna be there and I'm good for it. And I can count on me being there to do this, to perform, you know, whatever the task is, you know.
+00:29:24 Darius
+When we lightened our production schedule over the summer, I had a few text messages like, where's the episode? Because we were part of their routine at that point, you know? What was I gonna say? Well, you go, I lost my train of thought.
+00:29:39 Jordan
+Yeah, and even I've been thinking about myself, like I was, You'd be surprised how, like, just doing stuff and making stuff and putting things out, people will support you. Like, people you don't expect to support you will support you. Like, you know, I was at a party this weekend and somebody was like, oh, I never, I never see you, I never, I don't see your post anymore. Like, do you stop posting? Like, I was like, yeah, I can not stop posting on my feed. I just post my story on Instagram because, you know, Nobody sees your **** nobody likes your **** whatever. They're like, that's lame though. Like, I like your content. Like, you just stop posting. You know, I kind of look forward to seeing your stuff, you know? And I was like, well, I got to figure out what I'm going to do with my page. So until then, I just kind of stop using it, essentially.
+00:30:18 Darius
+What is it about the permanence of the grid that, because I never post on my grid either. And it's just because it's permanent. And I don't like, I like the fact that the story goes away.
+00:30:26 Jordan
+I don't know if it's like an anxiety thing or what it is. I'm not really sure. and also because I guess I just don't really know what to post anymore because we I post so much my story I'm like if I just posted on my feed you already saw it in my story so like that seems kind of redundant I don't know but I've been thinking about just like using that and converting that just like a poetry page and then just like posting that way I don't worry about hitting as many of mics and all that kind of stuff because like life and I got like transition going on right now and yeah but I've even tried to post more like on TikTok and like there is good feedback and people do like you know your the things that you make, there is an audience. And I think I know for me at least, like my brother told me this, he's like, it feels like when I see your content, it's like you want to be seen, but you don't want attention. And I was like, damn, you're kind of right. Cause like everybody has, you know, just a little bit of anxiety that comes with posting on the internet because you don't know people, people could like post one thing and you're just trying to be funny and people like, oh, you're weird, you know, **** like that, you know, that can get in your head sometimes. But it's better to have a million and one post than no ******* feed. You know what I'm saying?
+00:31:38 Darius
+Yeah, I, it's definitely, I don't like, I don't know if the word if it's a</t>
+  </si>
+  <si>
+    <t>Grab the Baton: Cookouts, Childhood Chaos &amp; Creative Discipline</t>
+  </si>
 </sst>
 </file>
 
@@ -9124,6 +9457,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9443,7 +9780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -10118,6 +10455,21 @@
         <v>256</v>
       </c>
       <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>265</v>
+      </c>
+      <c r="B41" t="s">
+        <v>262</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E41" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E40" xr:uid="{77C17E25-847F-43D6-AEDB-CD2A150F451C}"/>
@@ -10131,7 +10483,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -10700,6 +11052,20 @@
         <v>259</v>
       </c>
     </row>
+    <row r="41" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>265</v>
+      </c>
+      <c r="B41" t="s">
+        <v>262</v>
+      </c>
+      <c r="C41" t="s">
+        <v>262</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D40" xr:uid="{214257A5-E9A4-4538-96DF-EBCBFEE3F0D1}">
     <filterColumn colId="3">

--- a/WOOM Archive Inputs.xlsx
+++ b/WOOM Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE37E48-003A-4107-AB1F-4D2DCBCFB419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77F0F4C-3227-4039-B16A-105F00E45DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF7F1007-203D-4DE6-BF2A-5A27FA14567C}"/>
   </bookViews>
   <sheets>
     <sheet name="WOOM Archive" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="267">
   <si>
     <t>youtube_link</t>
   </si>
@@ -9005,48 +9005,6 @@
     <t>09.08.26</t>
   </si>
   <si>
-    <t>Topics Covered
-• DaBaby's Charlotte food truck, IG restaurant culture, and whether any food is worth a three-hour wait 
-• Funny childhood decisions that probably terrified their parents 
-• Running away as a joke, dangerous sledding, trampoline stunts, stair surfing, and neighborhood mischief 
-• Family traditions that are disappearing and who is responsible for preserving them 
-• Millennials inheriting the responsibilities once handled by parents, grandparents, aunts, and uncles 
-• Analysis paralysis versus taking action and building momentum through consistency 
-• Podcasting, audience-building, and becoming part of someone's routine 
-• Posting content online, social media anxiety, and worrying about public judgment 
-• Whether hobbies should become businesses or sources of income 
-• Influencer culture, authenticity, and the dangers of turning everything into content 
-Best Questions
-• Is there any restaurant worth standing in line three hours to eat at? 
-• What is the funniest thing you did as a child that terrified your parents? 
-• Which family traditions are actually worth preserving? 
-• Why do talented people get stuck while less-talented people succeed? 
-• Should hobbies be monetized? 
-• At what point does content creation stop being fun and start becoming work?
-Best Observations
-• Many traditions disappear not because older generations stop caring, but because younger generations never pick up the baton. 
-• Consistency often beats talent because people become part of their audience's routine. 
-• Most creators are terrible judges of what audiences will actually connect with. 
-• An unfinished project seen by people is usually more valuable than a perfect project that never leaves the hard drive. 
-• Social media rewards authenticity but simultaneously pressures creators toward performance. 
-• Many hobbies become less enjoyable when every moment is optimized for engagement and monetization. 
-Best Debate
-Should Hobbies Make Money?
-Jordan argued that there is nothing wrong with earning money from something you already love doing and that monetization can be a blessing when it happens naturally. Darius countered that commercialization can slowly drain enjoyment from a hobby and pointed to influencers who clearly no longer enjoy the content they create but continue because it has become their job.
-Themes
-• Childhood memories
-• Family traditions
-• Adulthood
-• Community responsibility
-• Consistency
-• Creativity
-• Podcasting
-• Social media
-• Content creation
-• Monetization
-• Influencer culture</t>
-  </si>
-  <si>
     <t>Transcript
 00:00:00 Darius
 We have to grab the baton. Traditions are dying out because we keep expecting the grownups to do it. But we're the grownups.
@@ -9333,6 +9291,63 @@
   </si>
   <si>
     <t>Grab the Baton: Cookouts, Childhood Chaos &amp; Creative Discipline</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Topics Covered&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;DaBaby&amp;#39;s Charlotte food truck, IG restaurant culture, and whether any food is worth a three-hour wait&lt;/li&gt;
+    &lt;li&gt;Funny childhood decisions that probably terrified their parents&lt;/li&gt;
+    &lt;li&gt;Running away as a joke, dangerous sledding, trampoline stunts, stair surfing, and neighborhood mischief&lt;/li&gt;
+    &lt;li&gt;Family traditions that are disappearing and who is responsible for preserving them&lt;/li&gt;
+    &lt;li&gt;Millennials inheriting the responsibilities once handled by parents, grandparents, aunts, and uncles&lt;/li&gt;
+    &lt;li&gt;Analysis paralysis versus taking action and building momentum through consistency&lt;/li&gt;
+    &lt;li&gt;Podcasting, audience-building, and becoming part of someone&amp;#39;s routine&lt;/li&gt;
+    &lt;li&gt;Posting content online, social media anxiety, and worrying about public judgment&lt;/li&gt;
+    &lt;li&gt;Whether hobbies should become businesses or sources of income&lt;/li&gt;
+    &lt;li&gt;Influencer culture, authenticity, and the dangers of turning everything into content&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Questions&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Is there any restaurant worth standing in line three hours to eat at?&lt;/li&gt;
+    &lt;li&gt;What is the funniest thing you did as a child that terrified your parents?&lt;/li&gt;
+    &lt;li&gt;Which family traditions are actually worth preserving?&lt;/li&gt;
+    &lt;li&gt;Why do talented people get stuck while less-talented people succeed?&lt;/li&gt;
+    &lt;li&gt;Should hobbies be monetized?&lt;/li&gt;
+    &lt;li&gt;At what point does content creation stop being fun and start becoming work?&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Observations&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Many traditions disappear not because older generations stop caring, but because younger generations never pick up the baton.&lt;/li&gt;
+    &lt;li&gt;Consistency often beats talent because people become part of their audience&amp;#39;s routine.&lt;/li&gt;
+    &lt;li&gt;Most creators are terrible judges of what audiences will actually connect with.&lt;/li&gt;
+    &lt;li&gt;An unfinished project seen by people is usually more valuable than a perfect project that never leaves the hard drive.&lt;/li&gt;
+    &lt;li&gt;Social media rewards authenticity but simultaneously pressures creators toward performance.&lt;/li&gt;
+    &lt;li&gt;Many hobbies become less enjoyable when every moment is optimized for engagement and monetization.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Best Debate&lt;/h3&gt;
+  &lt;p&gt;Should Hobbies Make Money? Jordan argued that there is nothing wrong with earning money from something you already love doing and that monetization can be a blessing when it happens naturally. Darius countered that commercialization can slowly drain enjoyment from a hobby and pointed to influencers who clearly no longer enjoy the content they create but continue because it has become their job.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Childhood memories&lt;/li&gt;
+      &lt;li&gt;Family traditions&lt;/li&gt;
+      &lt;li&gt;Adulthood&lt;/li&gt;
+      &lt;li&gt;Community responsibility&lt;/li&gt;
+      &lt;li&gt;Consistency&lt;/li&gt;
+      &lt;li&gt;Creativity&lt;/li&gt;
+      &lt;li&gt;Podcasting&lt;/li&gt;
+      &lt;li&gt;Social media&lt;/li&gt;
+      &lt;li&gt;Content creation&lt;/li&gt;
+      &lt;li&gt;Monetization&lt;/li&gt;
+      &lt;li&gt;Influencer culture&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
   </si>
 </sst>
 </file>
@@ -10458,16 +10473,16 @@
     </row>
     <row r="41" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B41" t="s">
         <v>262</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E41" s="5"/>
     </row>
@@ -11054,16 +11069,16 @@
     </row>
     <row r="41" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B41" t="s">
         <v>262</v>
       </c>
-      <c r="C41" t="s">
-        <v>262</v>
+      <c r="C41" s="7" t="s">
+        <v>266</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
